--- a/Program_Internships_Data.xlsx
+++ b/Program_Internships_Data.xlsx
@@ -745,6 +745,11 @@
           <t>Vansh Bansal</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="15.6" customHeight="1">
       <c r="C9" s="10" t="inlineStr">
@@ -773,6 +778,11 @@
           <t>Aman Kumar</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15.6" customHeight="1">
       <c r="C10" s="10" t="inlineStr">
@@ -801,6 +811,11 @@
           <t>Janvi</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>GMetrix</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="15.6" customHeight="1">
       <c r="C11" s="10" t="inlineStr">
@@ -829,6 +844,11 @@
           <t>Nikhil Kumar Jangir</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15.6" customHeight="1">
       <c r="C12" s="10" t="inlineStr">
@@ -857,6 +877,11 @@
           <t>Bhumika Punia</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>EVG Software Solutions Pvt. Ltd.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="15.6" customHeight="1">
       <c r="C13" s="10" t="inlineStr">
@@ -885,6 +910,11 @@
           <t>Alisha</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="15.6" customHeight="1">
       <c r="C14" s="10" t="inlineStr">
@@ -913,6 +943,11 @@
           <t>Charu sood</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Microsoft azure</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="15.6" customHeight="1">
       <c r="C15" s="10" t="inlineStr">
@@ -941,6 +976,11 @@
           <t>Suryansh Shandilya</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="15.6" customHeight="1">
       <c r="C16" s="10" t="inlineStr">
@@ -969,6 +1009,11 @@
           <t>Shruti Sharma</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Microsoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="15.6" customHeight="1">
       <c r="C17" s="10" t="inlineStr">
@@ -997,6 +1042,11 @@
           <t>Ashmit Thakur</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Salesforce {Pearson vue}</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="15.6" customHeight="1">
       <c r="C18" s="10" t="inlineStr">
@@ -1025,6 +1075,11 @@
           <t>Sanmati Jain</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>pearson</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="15.6" customHeight="1">
       <c r="C19" s="10" t="inlineStr">
@@ -1053,6 +1108,11 @@
           <t>Aarush Sharma</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MERN Stack</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="15.6" customHeight="1">
       <c r="C20" s="10" t="inlineStr">
@@ -1081,6 +1141,11 @@
           <t>Shivani Thakur</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="15.6" customHeight="1">
       <c r="C21" s="10" t="inlineStr">
@@ -1109,6 +1174,11 @@
           <t>Suryansh Shandilya</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="15.6" customHeight="1">
       <c r="C22" s="10" t="inlineStr">
@@ -1137,6 +1207,11 @@
           <t>Gautam Dhiman</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="15.6" customHeight="1">
       <c r="C23" s="10" t="inlineStr">
@@ -1165,6 +1240,11 @@
           <t>Prathana Kalai</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="15.6" customHeight="1">
       <c r="C24" s="10" t="inlineStr">
@@ -1193,6 +1273,11 @@
           <t>Harjasjot Singh Sidhu</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="15.6" customHeight="1">
       <c r="C25" s="10" t="inlineStr">
@@ -1221,6 +1306,11 @@
           <t>Sukhman Preet Singh</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Microsoft Certifification</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="15.6" customHeight="1">
       <c r="C26" s="10" t="inlineStr">
@@ -1249,6 +1339,11 @@
           <t>Prannoy Chandola</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="15.6" customHeight="1">
       <c r="C27" s="10" t="inlineStr">
@@ -1277,6 +1372,11 @@
           <t>Keshav Sharma</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="15.6" customHeight="1">
       <c r="C28" s="10" t="inlineStr">
@@ -1305,6 +1405,11 @@
           <t>Gursimran Singh</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="15.6" customHeight="1">
       <c r="C29" s="10" t="inlineStr">
@@ -1333,6 +1438,11 @@
           <t>Tanu</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="15.6" customHeight="1">
       <c r="C30" s="10" t="inlineStr">
@@ -1361,6 +1471,11 @@
           <t>Jasmeet Singh</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="15.6" customHeight="1">
       <c r="C31" s="10" t="inlineStr">
@@ -1389,6 +1504,11 @@
           <t>Kavya Jain</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="15.6" customHeight="1">
       <c r="C32" s="10" t="inlineStr">
@@ -1417,6 +1537,11 @@
           <t>Kritika Ruhela</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Microsoft Certified</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="15.6" customHeight="1">
       <c r="C33" s="10" t="inlineStr">
@@ -1445,6 +1570,11 @@
           <t>ANMOL SINGH</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="15.6" customHeight="1">
       <c r="C34" s="10" t="inlineStr">
@@ -1473,6 +1603,11 @@
           <t>Shivali</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="15.6" customHeight="1">
       <c r="C35" s="10" t="inlineStr">
@@ -1501,6 +1636,11 @@
           <t>Sameer Singh Rawat</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="15.6" customHeight="1">
       <c r="C36" s="10" t="inlineStr">
@@ -1529,6 +1669,11 @@
           <t>Gurmillan singh</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Microsoft certifications</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="15.6" customHeight="1">
       <c r="C37" s="10" t="inlineStr">
@@ -1557,6 +1702,11 @@
           <t>Bhavishya Kumar</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="15.6" customHeight="1">
       <c r="C38" s="10" t="inlineStr">
@@ -1585,6 +1735,11 @@
           <t>Parv Gupta</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="15.6" customHeight="1">
       <c r="C39" s="10" t="inlineStr">
@@ -1613,6 +1768,11 @@
           <t>NAMIT SHARMA</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Github Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="15.6" customHeight="1">
       <c r="C40" s="10" t="inlineStr">
@@ -1641,6 +1801,11 @@
           <t>Tanvi Gupta</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="15.6" customHeight="1">
       <c r="C41" s="10" t="inlineStr">
@@ -1669,6 +1834,11 @@
           <t>Anurag Mondal</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="15.6" customHeight="1">
       <c r="C42" s="10" t="inlineStr">
@@ -1697,6 +1867,11 @@
           <t>Mukul kumar</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Certiport, a Pearson VUE Business</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="15.6" customHeight="1">
       <c r="C43" s="10" t="inlineStr">
@@ -1725,6 +1900,11 @@
           <t>Umang Dokania</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="15.6" customHeight="1">
       <c r="C44" s="10" t="inlineStr">
@@ -1753,6 +1933,11 @@
           <t>Ridhiman Pirta</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="15.6" customHeight="1">
       <c r="C45" s="10" t="inlineStr">
@@ -1781,6 +1966,11 @@
           <t>Shashwat Yadav</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="C46" s="10" t="inlineStr">
@@ -1809,6 +1999,11 @@
           <t>Tanya Singla</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="C47" s="10" t="inlineStr">
@@ -1837,6 +2032,11 @@
           <t>Dhruvi</t>
         </is>
       </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="C48" s="10" t="inlineStr">
@@ -1865,6 +2065,11 @@
           <t>Suksham Raina</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="C49" s="10" t="inlineStr">
@@ -1893,6 +2098,11 @@
           <t>Suvani Kapila</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="C50" s="10" t="inlineStr">
@@ -1921,6 +2131,11 @@
           <t>Sanskar Sinha</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Microsoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="C51" s="10" t="inlineStr">
@@ -1949,6 +2164,11 @@
           <t>Prakriti Sharma</t>
         </is>
       </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Github Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="C52" s="10" t="inlineStr">
@@ -1977,6 +2197,11 @@
           <t>Deepjoy paul</t>
         </is>
       </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>pearson</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="C53" s="10" t="inlineStr">
@@ -2005,6 +2230,11 @@
           <t>Arpit pathania</t>
         </is>
       </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="C54" s="10" t="inlineStr">
@@ -2033,6 +2263,11 @@
           <t>Dhruvi</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="C55" s="10" t="inlineStr">
@@ -2061,6 +2296,11 @@
           <t>Sushmita Barman</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Microsoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="C56" s="10" t="inlineStr">
@@ -2089,6 +2329,11 @@
           <t>Suksham Raina</t>
         </is>
       </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="C57" s="10" t="inlineStr">
@@ -2117,6 +2362,11 @@
           <t>Shalok Dadhwal</t>
         </is>
       </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Microsoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="C58" s="10" t="inlineStr">
@@ -2145,6 +2395,11 @@
           <t>Rakshit Sawhney</t>
         </is>
       </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="C59" s="10" t="inlineStr">
@@ -2173,6 +2428,11 @@
           <t>Pranay Tiwari</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Tiwari Pranay</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="C60" s="10" t="inlineStr">
@@ -2201,6 +2461,11 @@
           <t>Ayush Sharma</t>
         </is>
       </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="C61" s="10" t="inlineStr">
@@ -2229,6 +2494,11 @@
           <t>ANURAG</t>
         </is>
       </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="C62" s="10" t="inlineStr">
@@ -2257,6 +2527,11 @@
           <t>Aditya</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>MICROSOFT</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="C63" s="10" t="inlineStr">
@@ -2285,6 +2560,11 @@
           <t>Kartik Karnwal</t>
         </is>
       </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="C64" s="10" t="inlineStr">
@@ -2313,6 +2593,11 @@
           <t>Abhijith N</t>
         </is>
       </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>AWS Training &amp; Certification</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="C65" s="10" t="inlineStr">
@@ -2341,6 +2626,11 @@
           <t>Dhruv Lakhlan</t>
         </is>
       </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Microsoft Certificate</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="C66" s="10" t="inlineStr">
@@ -2369,6 +2659,11 @@
           <t>Armaan Atri</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="C67" s="10" t="inlineStr">
@@ -2397,6 +2692,11 @@
           <t>Sanmati Jain</t>
         </is>
       </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>pearson</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="C68" s="10" t="inlineStr">
@@ -2425,6 +2725,11 @@
           <t>Priyanka</t>
         </is>
       </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="C69" s="10" t="inlineStr">
@@ -2453,6 +2758,11 @@
           <t>Devanshu Sharma</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="C70" s="10" t="inlineStr">
@@ -2481,6 +2791,11 @@
           <t>RAMNEEK KAUR</t>
         </is>
       </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="C71" s="10" t="inlineStr">
@@ -2509,6 +2824,11 @@
           <t>DARSHPREET SINGH</t>
         </is>
       </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Fortinet</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="C72" s="10" t="inlineStr">
@@ -2537,6 +2857,11 @@
           <t>Souradeep Banerjee</t>
         </is>
       </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="C73" s="10" t="inlineStr">
@@ -2565,6 +2890,11 @@
           <t>Sakhsham Sharma</t>
         </is>
       </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="C74" s="10" t="inlineStr">
@@ -2593,6 +2923,11 @@
           <t>Yash Garg</t>
         </is>
       </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>fortinet</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="C75" s="10" t="inlineStr">
@@ -2621,6 +2956,11 @@
           <t>Gautam Kumar</t>
         </is>
       </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="C76" s="10" t="inlineStr">
@@ -2649,6 +2989,11 @@
           <t>Sunandan Sharma</t>
         </is>
       </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="C77" s="10" t="inlineStr">
@@ -2677,6 +3022,11 @@
           <t>Aditya Bhandari</t>
         </is>
       </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="C78" s="10" t="inlineStr">
@@ -2705,6 +3055,11 @@
           <t>Aadarsh Ahlawat</t>
         </is>
       </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Chandigarh University</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="C79" s="10" t="inlineStr">
@@ -2733,6 +3088,11 @@
           <t>Sakhsham Sharma</t>
         </is>
       </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="C80" s="10" t="inlineStr">
@@ -2761,6 +3121,11 @@
           <t>Nishant Verma</t>
         </is>
       </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Fortinet</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="C81" s="10" t="inlineStr">
@@ -2789,6 +3154,11 @@
           <t>Anika Sharma</t>
         </is>
       </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Microsoft certifications</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="C82" s="10" t="inlineStr">
@@ -2817,6 +3187,11 @@
           <t>Vriddhi kakkar</t>
         </is>
       </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Chandigarh University</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="C83" s="10" t="inlineStr">
@@ -2845,6 +3220,11 @@
           <t>Akshat Gupta</t>
         </is>
       </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Microsoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="C84" s="10" t="inlineStr">
@@ -2873,6 +3253,11 @@
           <t>V S Aarsha</t>
         </is>
       </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="C85" s="10" t="inlineStr">
@@ -2901,6 +3286,11 @@
           <t>Hardik Kumar</t>
         </is>
       </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="C86" s="10" t="inlineStr">
@@ -2929,6 +3319,11 @@
           <t>Garvit</t>
         </is>
       </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Microsoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="C87" s="10" t="inlineStr">
@@ -2957,6 +3352,11 @@
           <t>Vasu Bansal</t>
         </is>
       </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="C88" s="10" t="inlineStr">
@@ -2985,6 +3385,11 @@
           <t>ASHOK CHATURVEDI</t>
         </is>
       </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="C89" s="10" t="inlineStr">
@@ -3013,6 +3418,11 @@
           <t>Akshit Gautam</t>
         </is>
       </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="C90" s="10" t="inlineStr">
@@ -3041,6 +3451,11 @@
           <t>Asmita Singh</t>
         </is>
       </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="C91" s="10" t="inlineStr">
@@ -3069,6 +3484,11 @@
           <t>Sakshi KUmari</t>
         </is>
       </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="C92" s="10" t="inlineStr">
@@ -3097,6 +3517,11 @@
           <t>Yugam</t>
         </is>
       </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Microsoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="C93" s="10" t="inlineStr">
@@ -3125,6 +3550,11 @@
           <t>Sukhjinder Singh</t>
         </is>
       </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="C94" s="10" t="inlineStr">
@@ -3153,6 +3583,11 @@
           <t>Pulastaya Bansal</t>
         </is>
       </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="C95" s="10" t="inlineStr">
@@ -3181,6 +3616,11 @@
           <t>Bhawika</t>
         </is>
       </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Fortinet Training Institute</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="C96" s="10" t="inlineStr">
@@ -3209,6 +3649,11 @@
           <t>Vaidehi Sharma</t>
         </is>
       </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="C97" s="10" t="inlineStr">
@@ -3237,6 +3682,11 @@
           <t>Nischaya Garg</t>
         </is>
       </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="C98" s="10" t="inlineStr">
@@ -3265,6 +3715,11 @@
           <t>Yuvraj Singh</t>
         </is>
       </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Er. Santosh Kumar, Dr. Sandeep Singh Kang</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="C99" s="10" t="inlineStr">
@@ -3293,6 +3748,11 @@
           <t>Dhanyasai Supraja</t>
         </is>
       </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="C100" s="10" t="inlineStr">
@@ -3321,6 +3781,11 @@
           <t>Nikunj Jain</t>
         </is>
       </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>GITHUB</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="C101" s="10" t="inlineStr">
@@ -3349,6 +3814,11 @@
           <t>Jatin Verma</t>
         </is>
       </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Microsoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="C102" s="10" t="inlineStr">
@@ -3377,6 +3847,11 @@
           <t>Ansh Soni</t>
         </is>
       </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="C103" s="10" t="inlineStr">
@@ -3405,6 +3880,11 @@
           <t>Rijuta Sharma</t>
         </is>
       </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>CISCO</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="C104" s="10" t="inlineStr">
@@ -3433,6 +3913,11 @@
           <t>harsh</t>
         </is>
       </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>CCNA</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="C105" s="10" t="inlineStr">
@@ -3461,6 +3946,11 @@
           <t>Anshu Kumar</t>
         </is>
       </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Tricon Infotech</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="C106" s="10" t="inlineStr">
@@ -3489,6 +3979,11 @@
           <t>Anna</t>
         </is>
       </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="C107" s="10" t="inlineStr">
@@ -3517,6 +4012,11 @@
           <t>Jnaneswar Kandukuri</t>
         </is>
       </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Fortinet Certified Associate</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="C108" s="10" t="inlineStr">
@@ -3545,6 +4045,11 @@
           <t>HARSH KUMAR</t>
         </is>
       </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="C109" s="10" t="inlineStr">
@@ -3573,6 +4078,11 @@
           <t>Lakshay Raina</t>
         </is>
       </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Fortinet</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="C110" s="10" t="inlineStr">
@@ -3601,6 +4111,11 @@
           <t>Ms. Garima Singh</t>
         </is>
       </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="C111" s="10" t="inlineStr">
@@ -3629,6 +4144,11 @@
           <t>Anshu Sharma</t>
         </is>
       </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="C112" s="10" t="inlineStr">
@@ -3657,6 +4177,11 @@
           <t>Kavisha Sharma</t>
         </is>
       </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Mircrosoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="C113" s="10" t="inlineStr">
@@ -3685,6 +4210,11 @@
           <t>Jatin Chadda</t>
         </is>
       </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="C114" s="10" t="inlineStr">
@@ -3713,6 +4243,11 @@
           <t>Karan Pratap Singh</t>
         </is>
       </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="C115" s="10" t="inlineStr">
@@ -3741,6 +4276,11 @@
           <t>Pratham Singhal</t>
         </is>
       </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="C116" s="10" t="inlineStr">
@@ -3769,6 +4309,11 @@
           <t>Manjot Singh</t>
         </is>
       </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Pearson - Information Technology Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="C117" s="10" t="inlineStr">
@@ -3797,6 +4342,11 @@
           <t>Divyanshu Kumar</t>
         </is>
       </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Microsoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="C118" s="10" t="inlineStr">
@@ -3825,6 +4375,11 @@
           <t>HARSH BHARDWAJ</t>
         </is>
       </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="C119" s="10" t="inlineStr">
@@ -3853,6 +4408,11 @@
           <t>THORATI MADHAVA DEEP KUMAR</t>
         </is>
       </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>corizo</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="C120" s="10" t="inlineStr">
@@ -3881,6 +4441,11 @@
           <t>Saksham Beniwal</t>
         </is>
       </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="C121" s="10" t="inlineStr">
@@ -3909,6 +4474,11 @@
           <t>Kabir</t>
         </is>
       </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="C122" s="10" t="inlineStr">
@@ -3937,6 +4507,11 @@
           <t>Mayengbam Devasis Singh</t>
         </is>
       </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Github</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="C123" s="10" t="inlineStr">
@@ -3965,6 +4540,11 @@
           <t>NIKUNJ JAIN</t>
         </is>
       </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>GITHUB</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="C124" s="10" t="inlineStr">
@@ -3993,6 +4573,11 @@
           <t>ADITI SHUKLA</t>
         </is>
       </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="C125" s="10" t="inlineStr">
@@ -4021,6 +4606,11 @@
           <t>Aaryan Gill</t>
         </is>
       </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="C126" s="10" t="inlineStr">
@@ -4049,6 +4639,11 @@
           <t>R. Grushnesh</t>
         </is>
       </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="C127" s="10" t="inlineStr">
@@ -4077,6 +4672,11 @@
           <t>Abhijeet</t>
         </is>
       </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="C128" s="10" t="inlineStr">
@@ -4105,6 +4705,11 @@
           <t>Gitansh Gupta</t>
         </is>
       </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="C129" s="10" t="inlineStr">
@@ -4133,6 +4738,11 @@
           <t>Gunveen Kaur</t>
         </is>
       </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>BLS INTERNATIONAL</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="C130" s="10" t="inlineStr">
@@ -4161,6 +4771,11 @@
           <t>Ankitt</t>
         </is>
       </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="C131" s="10" t="inlineStr">
@@ -4189,6 +4804,11 @@
           <t>Ridhi</t>
         </is>
       </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="C132" s="10" t="inlineStr">
@@ -4217,6 +4837,11 @@
           <t>Himanshu</t>
         </is>
       </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="C133" s="10" t="inlineStr">
@@ -4245,6 +4870,11 @@
           <t>Rishabh Raikwar</t>
         </is>
       </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>The Azure AI Fundamentals certification is officially issued by Microsoft, as it is a recognized Microsoft credential verified through Certiport (verify.certiport.com).  Certification Name: Azure AI Fundamentals Issuing Authority: Microsoft Date Issued: November 3, 2025 Verification ID: LM4Q-s4wW</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="C134" s="10" t="inlineStr">
@@ -4273,6 +4903,11 @@
           <t>Subhayu Mukherjee</t>
         </is>
       </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Fortinet</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="C135" s="10" t="inlineStr">
@@ -4301,6 +4936,11 @@
           <t>Harinder  singh</t>
         </is>
       </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="C136" s="10" t="inlineStr">
@@ -4329,6 +4969,11 @@
           <t>Yash Tanwar</t>
         </is>
       </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="C137" s="10" t="inlineStr">
@@ -4357,6 +5002,11 @@
           <t>Karan Pratatap Singh</t>
         </is>
       </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="C138" s="10" t="inlineStr">
@@ -4385,6 +5035,11 @@
           <t>Divyam Arora</t>
         </is>
       </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="C139" s="10" t="inlineStr">
@@ -4413,6 +5068,11 @@
           <t>Shruti</t>
         </is>
       </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="C140" s="10" t="inlineStr">
@@ -4441,6 +5101,11 @@
           <t>Paras</t>
         </is>
       </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="C141" s="10" t="inlineStr">
@@ -4469,6 +5134,11 @@
           <t>Vasu Thakral</t>
         </is>
       </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="C142" s="10" t="inlineStr">
@@ -4497,6 +5167,11 @@
           <t>Sakshi Singh</t>
         </is>
       </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Expertia AI Technologies Pvt. Ltd., Bangalore</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="C143" s="10" t="inlineStr">
@@ -4525,6 +5200,11 @@
           <t>Aditi Parmar</t>
         </is>
       </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Microsoft azure</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="C144" s="10" t="inlineStr">
@@ -4553,6 +5233,11 @@
           <t>Tanmoy Talukdar</t>
         </is>
       </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Microsoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="C145" s="10" t="inlineStr">
@@ -4581,6 +5266,11 @@
           <t>Hitanshu Kandpal</t>
         </is>
       </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="C146" s="10" t="inlineStr">
@@ -4609,6 +5299,11 @@
           <t>Arnav Srivastava</t>
         </is>
       </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="C147" s="10" t="inlineStr">
@@ -4637,6 +5332,11 @@
           <t>Manjot Singh</t>
         </is>
       </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Github Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="C148" s="10" t="inlineStr">
@@ -4665,6 +5365,11 @@
           <t>Riya kashyap</t>
         </is>
       </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Microsoft certifications</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="C149" s="10" t="inlineStr">
@@ -4693,6 +5398,11 @@
           <t>Aditya Kumar Yadav</t>
         </is>
       </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="C150" s="10" t="inlineStr">
@@ -4721,6 +5431,11 @@
           <t>Manav Agarwal</t>
         </is>
       </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Microsoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="C151" s="10" t="inlineStr">
@@ -4749,6 +5464,11 @@
           <t>Harsh Partap Jain</t>
         </is>
       </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Microsoft Certified</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="C152" s="10" t="inlineStr">
@@ -4777,6 +5497,11 @@
           <t>Sai Shashank Singu</t>
         </is>
       </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="C153" s="10" t="inlineStr">
@@ -4805,6 +5530,11 @@
           <t>Shiva Sharma</t>
         </is>
       </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="C154" s="10" t="inlineStr">
@@ -4833,6 +5563,11 @@
           <t>Bhawika Bhandari</t>
         </is>
       </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Aspen</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="C155" s="10" t="inlineStr">
@@ -4861,6 +5596,11 @@
           <t>Manav Agarwal</t>
         </is>
       </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Microsoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="C156" s="10" t="inlineStr">
@@ -4889,6 +5629,11 @@
           <t>Saurabh Rana</t>
         </is>
       </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="C157" s="10" t="inlineStr">
@@ -4917,6 +5662,11 @@
           <t>Yash gawali</t>
         </is>
       </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="C158" s="10" t="inlineStr">
@@ -4945,6 +5695,11 @@
           <t>Jatin Verma</t>
         </is>
       </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Microsoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="C159" s="10" t="inlineStr">
@@ -4973,6 +5728,11 @@
           <t>B.omprakash reddy</t>
         </is>
       </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="C160" s="10" t="inlineStr">
@@ -5001,6 +5761,11 @@
           <t>Nitin Sharma</t>
         </is>
       </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="C161" s="10" t="inlineStr">
@@ -5029,6 +5794,11 @@
           <t>Himtaj Singh</t>
         </is>
       </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>ThinkNEXT Technologies Limited</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="C162" s="10" t="inlineStr">
@@ -5057,6 +5827,11 @@
           <t>Soumil Lathey</t>
         </is>
       </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Microsoft certifications</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="C163" s="10" t="inlineStr">
@@ -5085,6 +5860,11 @@
           <t>Ayush Kumar Singh</t>
         </is>
       </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Github Foundation</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="C164" s="10" t="inlineStr">
@@ -5113,6 +5893,11 @@
           <t>RISHABH RAIKWAR</t>
         </is>
       </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>The Azure AI Fundamentals certification is officially issued by Microsoft, as it is a recognized Microsoft credential verified through Certiport (verify.certiport.com).  Certification Name: Azure AI Fundamentals Issuing Authority: Microsoft Date Issued: November 3, 2025 Verification ID: LM4Q-s4wW</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="C165" s="10" t="inlineStr">
@@ -5141,6 +5926,11 @@
           <t>Pallav Dhariwal</t>
         </is>
       </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="C166" s="10" t="inlineStr">
@@ -5169,6 +5959,11 @@
           <t>Harsh Partap Jain</t>
         </is>
       </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Microsoft Certified</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="C167" s="10" t="inlineStr">
@@ -5197,6 +5992,11 @@
           <t>Piyush Kalyan</t>
         </is>
       </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="C168" s="10" t="inlineStr">
@@ -5225,6 +6025,11 @@
           <t>Daksh Arora</t>
         </is>
       </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="C169" s="10" t="inlineStr">
@@ -5253,6 +6058,11 @@
           <t>Raveena</t>
         </is>
       </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Github</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="C170" s="10" t="inlineStr">
@@ -5281,6 +6091,11 @@
           <t>Lagan Arora</t>
         </is>
       </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Department of CSE at Chandigarh University</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="C171" s="10" t="inlineStr">
@@ -5309,6 +6124,11 @@
           <t>Rishi jain</t>
         </is>
       </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="C172" s="10" t="inlineStr">
@@ -5337,6 +6157,11 @@
           <t>Himanshi</t>
         </is>
       </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="C173" s="10" t="inlineStr">
@@ -5365,6 +6190,11 @@
           <t>Jaskaran Singh</t>
         </is>
       </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="C174" s="10" t="inlineStr">
@@ -5393,6 +6223,11 @@
           <t>Sujal jain</t>
         </is>
       </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="C175" s="10" t="inlineStr">
@@ -5421,6 +6256,11 @@
           <t>Dipanshu</t>
         </is>
       </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="C176" s="10" t="inlineStr">
@@ -5449,6 +6289,11 @@
           <t>Mokshda Sharma</t>
         </is>
       </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="C177" s="10" t="inlineStr">
@@ -5477,6 +6322,11 @@
           <t>Mansi Verma</t>
         </is>
       </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="C178" s="10" t="inlineStr">
@@ -5505,6 +6355,11 @@
           <t>Avin Mehla</t>
         </is>
       </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Github</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="C179" s="10" t="inlineStr">
@@ -5533,6 +6388,11 @@
           <t>Amgad Abudllah Noman Alharazi</t>
         </is>
       </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="C180" s="10" t="inlineStr">
@@ -5561,6 +6421,11 @@
           <t>Prashant</t>
         </is>
       </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>SALESFORCE</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="C181" s="10" t="inlineStr">
@@ -5589,6 +6454,11 @@
           <t>Piyush Nanda</t>
         </is>
       </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="C182" s="10" t="inlineStr">
@@ -5617,6 +6487,11 @@
           <t>Bijjam Sai Venkata Sudheer Reddy</t>
         </is>
       </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Fortinet Training Institute</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="C183" s="10" t="inlineStr">
@@ -5645,6 +6520,11 @@
           <t>Chandan Kumar</t>
         </is>
       </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="C184" s="10" t="inlineStr">
@@ -5673,6 +6553,11 @@
           <t>Virappan Baralu</t>
         </is>
       </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="C185" s="10" t="inlineStr">
@@ -5701,6 +6586,11 @@
           <t>Srinath Doggala</t>
         </is>
       </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Fortinet Training Institute</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="C186" s="10" t="inlineStr">
@@ -5729,6 +6619,11 @@
           <t>Adarsh Kumar</t>
         </is>
       </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="C187" s="10" t="inlineStr">
@@ -5757,6 +6652,11 @@
           <t>Jaya Prakash</t>
         </is>
       </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Fortinet Training Institute</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="C188" s="10" t="inlineStr">
@@ -5785,6 +6685,11 @@
           <t>Rohit Yadav</t>
         </is>
       </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="C189" s="10" t="inlineStr">
@@ -5813,6 +6718,11 @@
           <t>Kartik</t>
         </is>
       </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>GitHub Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="C190" s="10" t="inlineStr">
@@ -5841,6 +6751,11 @@
           <t>MEDHA SINGH</t>
         </is>
       </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="C191" s="10" t="inlineStr">
@@ -5869,6 +6784,11 @@
           <t>Harsh</t>
         </is>
       </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="C192" s="10" t="inlineStr">
@@ -5897,6 +6817,11 @@
           <t>Bianca Malhotra</t>
         </is>
       </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="C193" s="10" t="inlineStr">
@@ -5925,6 +6850,11 @@
           <t>Karan</t>
         </is>
       </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="C194" s="10" t="inlineStr">
@@ -5953,6 +6883,11 @@
           <t>Atul kumar</t>
         </is>
       </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="C195" s="10" t="inlineStr">
@@ -5981,6 +6916,11 @@
           <t>Ayush Choudhary</t>
         </is>
       </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Microsoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="C196" s="10" t="inlineStr">
@@ -6009,6 +6949,11 @@
           <t>HARDIK</t>
         </is>
       </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="C197" s="10" t="inlineStr">
@@ -6037,6 +6982,11 @@
           <t>TANISHA SINGH</t>
         </is>
       </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="C198" s="10" t="inlineStr">
@@ -6065,6 +7015,11 @@
           <t>Himanshi Mittal</t>
         </is>
       </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="C199" s="10" t="inlineStr">
@@ -6093,6 +7048,11 @@
           <t>gautam sharma</t>
         </is>
       </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="C200" s="10" t="inlineStr">
@@ -6121,6 +7081,11 @@
           <t>Ankit Chauhan</t>
         </is>
       </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="C201" s="10" t="inlineStr">
@@ -6149,6 +7114,11 @@
           <t>ATHARV sharma</t>
         </is>
       </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="C202" s="10" t="inlineStr">
@@ -6177,6 +7147,11 @@
           <t>Dasari Bhanu Prasad</t>
         </is>
       </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Microsoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="C203" s="10" t="inlineStr">
@@ -6205,6 +7180,11 @@
           <t>Akshat</t>
         </is>
       </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="C204" s="10" t="inlineStr">
@@ -6233,6 +7213,11 @@
           <t>Sanyam singla</t>
         </is>
       </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Github</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="C205" s="10" t="inlineStr">
@@ -6261,6 +7246,11 @@
           <t>Aman</t>
         </is>
       </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="C206" s="10" t="inlineStr">
@@ -6289,6 +7279,11 @@
           <t>Chirag</t>
         </is>
       </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="C207" s="10" t="inlineStr">
@@ -6317,6 +7312,11 @@
           <t>Ashita Sharma</t>
         </is>
       </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="C208" s="10" t="inlineStr">
@@ -6345,6 +7345,11 @@
           <t>Subhradip Majumder</t>
         </is>
       </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="C209" s="10" t="inlineStr">
@@ -6373,6 +7378,11 @@
           <t>Ayush yadav</t>
         </is>
       </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="C210" s="10" t="inlineStr">
@@ -6401,6 +7411,11 @@
           <t>Madhav</t>
         </is>
       </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="C211" s="10" t="inlineStr">
@@ -6429,6 +7444,11 @@
           <t>FATHIMATHU RUSFIDA</t>
         </is>
       </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="C212" s="10" t="inlineStr">
@@ -6457,6 +7477,11 @@
           <t>Tanishq Ahuja</t>
         </is>
       </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Git Hub</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="C213" s="10" t="inlineStr">
@@ -6485,6 +7510,11 @@
           <t>Sudheer Kumar</t>
         </is>
       </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Microsoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="C214" s="10" t="inlineStr">
@@ -6513,6 +7543,11 @@
           <t>Lakshay Goel</t>
         </is>
       </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Pearson IT Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="C215" s="10" t="inlineStr">
@@ -6541,6 +7576,11 @@
           <t>Ishwar Dagar</t>
         </is>
       </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="C216" s="10" t="inlineStr">
@@ -6569,6 +7609,11 @@
           <t>Taranjot Singh</t>
         </is>
       </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="C217" s="10" t="inlineStr">
@@ -6597,6 +7642,11 @@
           <t>Daksh</t>
         </is>
       </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Microsoft Certications</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="C218" s="10" t="inlineStr">
@@ -6625,6 +7675,11 @@
           <t>GURREDDY SATHYAVARDHAN REDDY</t>
         </is>
       </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>GitHub (through GitHub Education Program)</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="C219" s="10" t="inlineStr">
@@ -6653,6 +7708,11 @@
           <t>Rachit Jha</t>
         </is>
       </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="C220" s="10" t="inlineStr">
@@ -6681,6 +7741,11 @@
           <t>Vivan</t>
         </is>
       </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Date Issued: November 3, 2025</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="C221" s="10" t="inlineStr">
@@ -6709,6 +7774,11 @@
           <t>Ishant Singh</t>
         </is>
       </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="C222" s="10" t="inlineStr">
@@ -6737,6 +7807,11 @@
           <t>SHRESHTA</t>
         </is>
       </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Microsoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="C223" s="10" t="inlineStr">
@@ -6765,6 +7840,11 @@
           <t>Myla Vizwal Rathod</t>
         </is>
       </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Fortinet Training Institution</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="C224" s="10" t="inlineStr">
@@ -6793,6 +7873,11 @@
           <t>Ujjansh Sundram</t>
         </is>
       </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="C225" s="10" t="inlineStr">
@@ -6821,6 +7906,11 @@
           <t>Jahnvi</t>
         </is>
       </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="C226" s="10" t="inlineStr">
@@ -6849,6 +7939,11 @@
           <t>Ayush Kumar</t>
         </is>
       </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="C227" s="10" t="inlineStr">
@@ -6877,6 +7972,11 @@
           <t>DHANA SRI RAM PANDURI</t>
         </is>
       </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="C228" s="10" t="inlineStr">
@@ -6905,6 +8005,11 @@
           <t>T S Naga Venkata Surya Teja</t>
         </is>
       </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="C229" s="10" t="inlineStr">
@@ -6933,6 +8038,11 @@
           <t>Anisha Kumari</t>
         </is>
       </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="C230" s="10" t="inlineStr">
@@ -6961,6 +8071,11 @@
           <t>Paramjeet Thakur</t>
         </is>
       </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="C231" s="10" t="inlineStr">
@@ -6989,6 +8104,11 @@
           <t>KV LOKESH</t>
         </is>
       </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="C232" s="10" t="inlineStr">
@@ -7017,6 +8137,11 @@
           <t>Amandeep</t>
         </is>
       </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="C233" s="10" t="inlineStr">
@@ -7045,6 +8170,11 @@
           <t>Suhani Rawat</t>
         </is>
       </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="C234" s="10" t="inlineStr">
@@ -7073,6 +8203,11 @@
           <t>Kumar Aditya</t>
         </is>
       </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Microsoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="C235" s="10" t="inlineStr">
@@ -7101,6 +8236,11 @@
           <t>P Vaishnavi</t>
         </is>
       </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="C236" s="10" t="inlineStr">
@@ -7129,6 +8269,11 @@
           <t>Abhinav Gupta</t>
         </is>
       </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="C237" s="10" t="inlineStr">
@@ -7157,6 +8302,11 @@
           <t>Gurkirat Singh</t>
         </is>
       </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="C238" s="10" t="inlineStr">
@@ -7185,6 +8335,11 @@
           <t>Vansh Sharma</t>
         </is>
       </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="C239" s="10" t="inlineStr">
@@ -7213,6 +8368,11 @@
           <t>Dhairya Sharma</t>
         </is>
       </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Microsoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="C240" s="10" t="inlineStr">
@@ -7241,6 +8401,11 @@
           <t>Aryan Singh</t>
         </is>
       </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="C241" s="10" t="inlineStr">
@@ -7269,6 +8434,11 @@
           <t>Anmol Rai</t>
         </is>
       </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="C242" s="10" t="inlineStr">
@@ -7297,6 +8467,11 @@
           <t>Prakhar Nautiyal</t>
         </is>
       </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="C243" s="10" t="inlineStr">
@@ -7325,6 +8500,11 @@
           <t>Uday Kapila</t>
         </is>
       </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="C244" s="10" t="inlineStr">
@@ -7353,6 +8533,11 @@
           <t>Kunal Singh</t>
         </is>
       </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="C245" s="10" t="inlineStr">
@@ -7381,6 +8566,11 @@
           <t>Lovejeet Patel</t>
         </is>
       </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="C246" s="10" t="inlineStr">
@@ -7409,6 +8599,11 @@
           <t>Shivansh Kutlehria</t>
         </is>
       </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>microsoft certifications</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="C247" s="10" t="inlineStr">
@@ -7437,6 +8632,11 @@
           <t>Aditya Mehta</t>
         </is>
       </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="C248" s="10" t="inlineStr">
@@ -7465,6 +8665,11 @@
           <t>Ravkirat Singh</t>
         </is>
       </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Microsoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="C249" s="10" t="inlineStr">
@@ -7493,6 +8698,11 @@
           <t>Manish Yadav</t>
         </is>
       </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="C250" s="10" t="inlineStr">
@@ -7521,6 +8731,11 @@
           <t>Adarsh Kumar</t>
         </is>
       </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Fortinet</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="C251" s="10" t="inlineStr">
@@ -7549,6 +8764,11 @@
           <t>Shashish Shekhar Kalia</t>
         </is>
       </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="C252" s="10" t="inlineStr">
@@ -7577,6 +8797,11 @@
           <t>Ankit Kumar</t>
         </is>
       </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="C253" s="10" t="inlineStr">
@@ -7605,6 +8830,11 @@
           <t>Karamjodh Singh</t>
         </is>
       </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="C254" s="10" t="inlineStr">
@@ -7633,6 +8863,11 @@
           <t>KOYENA GHOSH</t>
         </is>
       </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="C255" s="10" t="inlineStr">
@@ -7661,6 +8896,11 @@
           <t>Aamarsh Thakur</t>
         </is>
       </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="C256" s="10" t="inlineStr">
@@ -7689,6 +8929,11 @@
           <t>Ujjwal Sharma</t>
         </is>
       </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="C257" s="10" t="inlineStr">
@@ -7717,6 +8962,11 @@
           <t>RAKSHIT JARYAL</t>
         </is>
       </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Fortinet</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="C258" s="10" t="inlineStr">
@@ -7745,6 +8995,11 @@
           <t>Manav Sharma</t>
         </is>
       </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Microsoft Certificates</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="C259" s="10" t="inlineStr">
@@ -7773,6 +9028,11 @@
           <t>SHAIK ANAS</t>
         </is>
       </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="C260" s="10" t="inlineStr">
@@ -7801,6 +9061,11 @@
           <t>Jobanjot Singh Grewal</t>
         </is>
       </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="C261" s="10" t="inlineStr">
@@ -7829,6 +9094,11 @@
           <t>Harshvardhan Sharma</t>
         </is>
       </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="C262" s="10" t="inlineStr">
@@ -7857,6 +9127,11 @@
           <t>Kushagra Chakraborty</t>
         </is>
       </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>Certiport</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="C263" s="10" t="inlineStr">
@@ -7885,6 +9160,11 @@
           <t>Pranjali Gupta</t>
         </is>
       </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="C264" s="10" t="inlineStr">
@@ -7913,6 +9193,11 @@
           <t>Parmveer Singh</t>
         </is>
       </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="C265" s="10" t="inlineStr">
@@ -7941,6 +9226,11 @@
           <t>Bedika Punshi</t>
         </is>
       </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="C266" s="10" t="inlineStr">
@@ -7969,6 +9259,11 @@
           <t>Ashutosh kr. chaubey</t>
         </is>
       </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="C267" s="10" t="inlineStr">
@@ -7997,6 +9292,11 @@
           <t>Pratik Singh</t>
         </is>
       </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="C268" s="10" t="inlineStr">
@@ -8025,6 +9325,11 @@
           <t>Parv Gupta</t>
         </is>
       </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="C269" s="10" t="inlineStr">
@@ -8053,6 +9358,11 @@
           <t>Shreeyansh Kumar</t>
         </is>
       </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="C270" s="10" t="inlineStr">
@@ -8081,6 +9391,11 @@
           <t>Vaishnav Lalit</t>
         </is>
       </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>Github</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="C271" s="10" t="inlineStr">
@@ -8109,6 +9424,11 @@
           <t>Krish Sharma</t>
         </is>
       </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="C272" s="10" t="inlineStr">
@@ -8137,6 +9457,11 @@
           <t>DIPTI SINHA</t>
         </is>
       </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="C273" s="10" t="inlineStr">
@@ -8165,6 +9490,11 @@
           <t>Gurmehar Kaur</t>
         </is>
       </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>Meander software pvt.ltd</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="C274" s="10" t="inlineStr">
@@ -8193,6 +9523,11 @@
           <t>Prathamesh Sidana</t>
         </is>
       </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="C275" s="10" t="inlineStr">
@@ -8221,6 +9556,11 @@
           <t>Aryan Sood</t>
         </is>
       </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="C276" s="10" t="inlineStr">
@@ -8249,6 +9589,11 @@
           <t>Martha Sravani</t>
         </is>
       </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Pearson vue</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="C277" s="10" t="inlineStr">
@@ -8277,6 +9622,11 @@
           <t>Kartik Dogra</t>
         </is>
       </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="C278" s="10" t="inlineStr">
@@ -8305,6 +9655,11 @@
           <t>Arya Bhat</t>
         </is>
       </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="C279" s="10" t="inlineStr">
@@ -8333,6 +9688,11 @@
           <t>Kanish Thakur</t>
         </is>
       </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="C280" s="10" t="inlineStr">
@@ -8361,6 +9721,11 @@
           <t>Balaji A</t>
         </is>
       </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="C281" s="10" t="inlineStr">
@@ -8389,6 +9754,11 @@
           <t>M.RITHIKA</t>
         </is>
       </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>MSME , ISO 9001:2015 Certified Company, IAF, KAB (Korea Accreditation Board) (International Accreditation Forum)</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="C282" s="10" t="inlineStr">
@@ -8417,6 +9787,11 @@
           <t>Yash Sharma</t>
         </is>
       </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Microsoft certification</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="C283" s="10" t="inlineStr">
@@ -8445,6 +9820,11 @@
           <t>Krrish Parashar</t>
         </is>
       </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Cisco Certified Support Technician (CCST) – Cybersecurity certification</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="C284" s="10" t="inlineStr">
@@ -8473,6 +9853,11 @@
           <t>GAUTHAM KRISHNA</t>
         </is>
       </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="C285" s="10" t="inlineStr">
@@ -8501,6 +9886,11 @@
           <t>Dheeraj VP</t>
         </is>
       </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="C286" s="10" t="inlineStr">
@@ -8529,6 +9919,11 @@
           <t>Ashutosh Saini</t>
         </is>
       </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>Unity</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="C287" s="10" t="inlineStr">
@@ -8557,6 +9952,11 @@
           <t>S S SNEHA</t>
         </is>
       </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>Microsoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="C288" s="10" t="inlineStr">
@@ -8585,6 +9985,11 @@
           <t>SATYAM GUPTA</t>
         </is>
       </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="C289" s="10" t="inlineStr">
@@ -8613,6 +10018,11 @@
           <t>Mohit Sharma</t>
         </is>
       </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>Pearson VUE</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="C290" s="10" t="inlineStr">
@@ -8641,6 +10051,11 @@
           <t>Manvi</t>
         </is>
       </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>Github</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="C291" s="10" t="inlineStr">
@@ -8669,6 +10084,11 @@
           <t>Kartik</t>
         </is>
       </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>GitHub Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="C292" s="10" t="inlineStr">
@@ -8697,6 +10117,11 @@
           <t>Puneet tanwar</t>
         </is>
       </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>Microsoft certification</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="C293" s="10" t="inlineStr">
@@ -8725,6 +10150,11 @@
           <t>Prabhanshu Pal</t>
         </is>
       </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="C294" s="10" t="inlineStr">
@@ -8753,6 +10183,11 @@
           <t>Arun Kumar Bhagat</t>
         </is>
       </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>PEARSON</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="C295" s="10" t="inlineStr">
@@ -8781,6 +10216,11 @@
           <t>SATYAM GUPTA</t>
         </is>
       </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="C296" s="10" t="inlineStr">
@@ -8809,6 +10249,11 @@
           <t>Shubham Upadhyay</t>
         </is>
       </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>Github</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="C297" s="10" t="inlineStr">
@@ -8837,6 +10282,11 @@
           <t>Anshu Yadav</t>
         </is>
       </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="C298" s="10" t="inlineStr">
@@ -8865,6 +10315,11 @@
           <t>Rudransh Agarwal</t>
         </is>
       </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="C299" s="10" t="inlineStr">
@@ -8893,6 +10348,11 @@
           <t>Ayush verma</t>
         </is>
       </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>MICROSOT AZURE AI FUNDAMENTAL</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="C300" s="10" t="inlineStr">
@@ -8921,6 +10381,11 @@
           <t>Radhika Singla</t>
         </is>
       </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="C301" s="10" t="inlineStr">
@@ -8949,6 +10414,11 @@
           <t>Manav singh</t>
         </is>
       </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="C302" s="10" t="inlineStr">
@@ -8977,6 +10447,11 @@
           <t>Mayank Singla</t>
         </is>
       </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>Certiport</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="C303" s="10" t="inlineStr">
@@ -9005,6 +10480,11 @@
           <t>Pratik Singh</t>
         </is>
       </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="C304" s="10" t="inlineStr">
@@ -9033,6 +10513,11 @@
           <t>vashist salar</t>
         </is>
       </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="C305" s="10" t="inlineStr">
@@ -9061,6 +10546,11 @@
           <t>Aakriti Narang</t>
         </is>
       </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="C306" s="10" t="inlineStr">
@@ -9089,6 +10579,11 @@
           <t>Anantpreet Singh Dhaliwal</t>
         </is>
       </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="C307" s="10" t="inlineStr">
@@ -9117,6 +10612,11 @@
           <t>Sehaj Sukhleen Singh</t>
         </is>
       </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>CISCO</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="C308" s="10" t="inlineStr">
@@ -9145,6 +10645,11 @@
           <t>Vanshdeep</t>
         </is>
       </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="C309" s="10" t="inlineStr">
@@ -9173,6 +10678,11 @@
           <t>Raghav soni</t>
         </is>
       </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>Microsoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="C310" s="10" t="inlineStr">
@@ -9201,6 +10711,11 @@
           <t>Uday Bhardwaj</t>
         </is>
       </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="C311" s="10" t="inlineStr">
@@ -9229,6 +10744,11 @@
           <t>Korivi Dhilly Srikanth Reddy</t>
         </is>
       </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="C312" s="10" t="inlineStr">
@@ -9257,6 +10777,11 @@
           <t>Kushagra Pandey</t>
         </is>
       </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="C313" s="10" t="inlineStr">
@@ -9285,6 +10810,11 @@
           <t>Nikhil Kumar</t>
         </is>
       </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="C314" s="10" t="inlineStr">
@@ -9313,6 +10843,11 @@
           <t>Pratham Singhal</t>
         </is>
       </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="C315" s="10" t="inlineStr">
@@ -9341,6 +10876,11 @@
           <t>Akshat Agrawal</t>
         </is>
       </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="C316" s="10" t="inlineStr">
@@ -9369,6 +10909,11 @@
           <t>Nihar Paladugula</t>
         </is>
       </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>MIcrosoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="C317" s="10" t="inlineStr">
@@ -9397,6 +10942,11 @@
           <t>M.SRAVANI</t>
         </is>
       </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>Pearson Vue</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="C318" s="10" t="inlineStr">
@@ -9425,6 +10975,11 @@
           <t>Divyansh manhas</t>
         </is>
       </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="C319" s="10" t="inlineStr">
@@ -9453,6 +11008,11 @@
           <t>Divyansh</t>
         </is>
       </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>Github</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="C320" s="10" t="inlineStr">
@@ -9481,6 +11041,11 @@
           <t>Shion Shibu</t>
         </is>
       </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="C321" s="10" t="inlineStr">
@@ -9509,6 +11074,11 @@
           <t>ROHITH KANKIPATI</t>
         </is>
       </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="C322" s="10" t="inlineStr">
@@ -9537,6 +11107,11 @@
           <t>Harshdeep Singh</t>
         </is>
       </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="C323" s="10" t="inlineStr">
@@ -9565,6 +11140,11 @@
           <t>Ritik</t>
         </is>
       </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>Expertia ai technologies pvt.ltd</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="C324" s="10" t="inlineStr">
@@ -9593,6 +11173,11 @@
           <t>Gitansh Gupta</t>
         </is>
       </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="C325" s="10" t="inlineStr">
@@ -9621,6 +11206,11 @@
           <t>Alok Kumar</t>
         </is>
       </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="C326" s="10" t="inlineStr">
@@ -9649,6 +11239,11 @@
           <t>Harshita Pandey</t>
         </is>
       </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="C327" s="10" t="inlineStr">
@@ -9677,6 +11272,11 @@
           <t>Varun</t>
         </is>
       </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>Microsoft certification</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="C328" s="10" t="inlineStr">
@@ -9705,6 +11305,11 @@
           <t>ASHISH</t>
         </is>
       </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>Microsoft Certified</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="C329" s="10" t="inlineStr">
@@ -9733,6 +11338,11 @@
           <t>Tushar</t>
         </is>
       </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="C330" s="10" t="inlineStr">
@@ -9761,6 +11371,11 @@
           <t>Palash Mathur</t>
         </is>
       </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>Apple Inc &amp; Certiport</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="C331" s="10" t="inlineStr">
@@ -9789,6 +11404,11 @@
           <t>Umang Kumar</t>
         </is>
       </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>Microsoft certifications</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="C332" s="10" t="inlineStr">
@@ -9817,6 +11437,11 @@
           <t>Chikkala Jaswanth</t>
         </is>
       </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="C333" s="10" t="inlineStr">
@@ -9845,6 +11470,11 @@
           <t>Arnav Mishra</t>
         </is>
       </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="C334" s="10" t="inlineStr">
@@ -9873,6 +11503,11 @@
           <t>Shalini Kush</t>
         </is>
       </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>Issuing Authority of Professional Certification: Aptron Solutions Pvt. Ltd., Gurgaon</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="C335" s="10" t="inlineStr">
@@ -9901,6 +11536,11 @@
           <t>Kartikeya Beniwal</t>
         </is>
       </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>Livekit + astrodocs</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="C336" s="10" t="inlineStr">
@@ -9929,6 +11569,11 @@
           <t>Shubham</t>
         </is>
       </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>Fortinet training institute</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="C337" s="10" t="inlineStr">
@@ -9957,6 +11602,11 @@
           <t>Parth</t>
         </is>
       </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>Pearson VUE</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="C338" s="10" t="inlineStr">
@@ -9985,6 +11635,11 @@
           <t>Agastya Vashisht</t>
         </is>
       </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="C339" s="10" t="inlineStr">
@@ -10013,6 +11668,11 @@
           <t>SALONI GUPTA</t>
         </is>
       </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>TATA STEEL</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="C340" s="10" t="inlineStr">
@@ -10041,6 +11701,11 @@
           <t>RAKSHIT RAJPUT</t>
         </is>
       </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>GirHub</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="C341" s="10" t="inlineStr">
@@ -10069,6 +11734,11 @@
           <t>kaaseenatha reddy</t>
         </is>
       </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>Fortinet Certified Associate in Cybersecurity</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="C342" s="10" t="inlineStr">
@@ -10097,6 +11767,11 @@
           <t>harsh</t>
         </is>
       </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>CCNA</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="C343" s="10" t="inlineStr">
@@ -10125,6 +11800,11 @@
           <t>anvesha</t>
         </is>
       </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="C344" s="10" t="inlineStr">
@@ -10153,6 +11833,11 @@
           <t>KARAN RANA</t>
         </is>
       </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>CISCO CERTIFIED SUPPORT TECHNICIAN - NETWORKING</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="C345" s="10" t="inlineStr">
@@ -10181,6 +11866,11 @@
           <t>Vanum Venkata Charan</t>
         </is>
       </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>Fortinet Certified Associate in Cybersecurity</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="C346" s="10" t="inlineStr">
@@ -10209,6 +11899,11 @@
           <t>Dasari Veera Venkata Nooka Surya Saran</t>
         </is>
       </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="C347" s="10" t="inlineStr">
@@ -10237,6 +11932,11 @@
           <t>Baivhav Kummar</t>
         </is>
       </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>Github</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="C348" s="10" t="inlineStr">
@@ -10265,6 +11965,11 @@
           <t>Samarth Raina</t>
         </is>
       </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>Certiport(Microsoft)</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="C349" s="10" t="inlineStr">
@@ -10293,6 +11998,11 @@
           <t>Ankita Joshi</t>
         </is>
       </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="C350" s="10" t="inlineStr">
@@ -10321,6 +12031,11 @@
           <t>Akshima Chanel</t>
         </is>
       </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="C351" s="10" t="inlineStr">
@@ -10349,6 +12064,11 @@
           <t>Raj Kumar</t>
         </is>
       </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="C352" s="10" t="inlineStr">
@@ -10377,6 +12097,11 @@
           <t>Anuj Yadav</t>
         </is>
       </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>Microsoft certifications</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="C353" s="10" t="inlineStr">
@@ -10405,6 +12130,11 @@
           <t>Shivangi Kumari</t>
         </is>
       </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="C354" s="10" t="inlineStr">
@@ -10433,6 +12163,11 @@
           <t>Lavish</t>
         </is>
       </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="C355" s="10" t="inlineStr">
@@ -10461,6 +12196,11 @@
           <t>Raj Gupta</t>
         </is>
       </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="C356" s="10" t="inlineStr">
@@ -10489,6 +12229,11 @@
           <t>Soumyadiya Ganguly</t>
         </is>
       </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="C357" s="10" t="inlineStr">
@@ -10517,6 +12262,11 @@
           <t>Yatin Singh</t>
         </is>
       </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>CISCO</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="C358" s="10" t="inlineStr">
@@ -10545,6 +12295,11 @@
           <t>Soumay Soni</t>
         </is>
       </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="C359" s="10" t="inlineStr">
@@ -10573,6 +12328,11 @@
           <t>Aryan Kohli</t>
         </is>
       </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="C360" s="10" t="inlineStr">
@@ -10601,6 +12361,11 @@
           <t>AYUSH VERMA</t>
         </is>
       </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>MICROSOT AZURE AI FUNDAMENTAL</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="C361" s="10" t="inlineStr">
@@ -10629,6 +12394,11 @@
           <t>RISHABH WADHWA</t>
         </is>
       </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>PEARSON</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="C362" s="10" t="inlineStr">
@@ -10657,6 +12427,11 @@
           <t>Nishant Verma</t>
         </is>
       </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>Fortinet</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="C363" s="10" t="inlineStr">
@@ -10685,6 +12460,11 @@
           <t>Jadav Sai Srujan</t>
         </is>
       </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="C364" s="10" t="inlineStr">
@@ -10713,6 +12493,11 @@
           <t>Nevia Sandhu</t>
         </is>
       </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>Microsoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="C365" s="10" t="inlineStr">
@@ -10741,6 +12526,11 @@
           <t>Abhishek Choudhary</t>
         </is>
       </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="C366" s="10" t="inlineStr">
@@ -10769,6 +12559,11 @@
           <t>Priyanshu Agarwal</t>
         </is>
       </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="C367" s="10" t="inlineStr">
@@ -10797,6 +12592,11 @@
           <t>Kabir</t>
         </is>
       </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="C368" s="10" t="inlineStr">
@@ -10825,6 +12625,11 @@
           <t>Shaily Chauhan</t>
         </is>
       </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>Github</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="C369" s="10" t="inlineStr">
@@ -10853,6 +12658,11 @@
           <t>Aryan Koundal</t>
         </is>
       </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>Fortinet</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="C370" s="10" t="inlineStr">
@@ -10881,6 +12691,11 @@
           <t>Mohammad Arzaul Haque</t>
         </is>
       </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>Salesforce Certified</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="C371" s="10" t="inlineStr">
@@ -10909,6 +12724,11 @@
           <t>Anish Kumar Singh</t>
         </is>
       </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>Fortinet</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="C372" s="10" t="inlineStr">
@@ -10937,6 +12757,11 @@
           <t>HARSH</t>
         </is>
       </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>micro soft</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="C373" s="10" t="inlineStr">
@@ -10965,6 +12790,11 @@
           <t>OM JI</t>
         </is>
       </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="C374" s="10" t="inlineStr">
@@ -10993,6 +12823,11 @@
           <t>S.Aadhithya</t>
         </is>
       </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>Microsoft Azure</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="C375" s="10" t="inlineStr">
@@ -11021,6 +12856,11 @@
           <t>Hashita Arora</t>
         </is>
       </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="C376" s="10" t="inlineStr">
@@ -11049,6 +12889,11 @@
           <t>AGAMPAL SINGH</t>
         </is>
       </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="C377" s="10" t="inlineStr">
@@ -11077,6 +12922,11 @@
           <t>Akhilesh Jethi</t>
         </is>
       </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="C378" s="10" t="inlineStr">
@@ -11105,6 +12955,11 @@
           <t>TusarRana</t>
         </is>
       </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>Xpressbites</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="C379" s="10" t="inlineStr">
@@ -11133,6 +12988,11 @@
           <t>AFRISH IBRAHIM A</t>
         </is>
       </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="C380" s="10" t="inlineStr">
@@ -11161,6 +13021,11 @@
           <t>Ashish Kumar Gupta</t>
         </is>
       </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>GitHub Foundation</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="C381" s="10" t="inlineStr">
@@ -11189,6 +13054,11 @@
           <t>Chhavi</t>
         </is>
       </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>Fortinet</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="C382" s="10" t="inlineStr">
@@ -11217,6 +13087,11 @@
           <t>Vanshika Jaiswal</t>
         </is>
       </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="C383" s="10" t="inlineStr">
@@ -11245,6 +13120,11 @@
           <t>Aayush Dhar</t>
         </is>
       </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="C384" s="10" t="inlineStr">
@@ -11273,6 +13153,11 @@
           <t>Kartik Minhas</t>
         </is>
       </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>Github Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="C385" s="10" t="inlineStr">
@@ -11301,6 +13186,11 @@
           <t>Lakshya Kohli</t>
         </is>
       </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="C386" s="10" t="inlineStr">
@@ -11329,6 +13219,11 @@
           <t>Aashmit Bhattacharjee</t>
         </is>
       </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>Fortinet</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="C387" s="10" t="inlineStr">
@@ -11357,6 +13252,11 @@
           <t>Sudipta Bhowmik</t>
         </is>
       </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="C388" s="10" t="inlineStr">
@@ -11385,6 +13285,11 @@
           <t>Baratam Sri Manikanta</t>
         </is>
       </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="C389" s="10" t="inlineStr">
@@ -11413,6 +13318,11 @@
           <t>Aryan</t>
         </is>
       </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>Microsoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="C390" s="10" t="inlineStr">
@@ -11441,6 +13351,11 @@
           <t>Hitesh Sharma</t>
         </is>
       </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>Microsoft Certified</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="C391" s="10" t="inlineStr">
@@ -11469,6 +13384,11 @@
           <t>Adarsh Kumar</t>
         </is>
       </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>Fortinet</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="C392" s="10" t="inlineStr">
@@ -11497,6 +13417,11 @@
           <t>Vishal Khatri</t>
         </is>
       </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="C393" s="10" t="inlineStr">
@@ -11525,6 +13450,11 @@
           <t>Shubham Sharma</t>
         </is>
       </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="C394" s="10" t="inlineStr">
@@ -11553,6 +13483,11 @@
           <t>Gudala Tejo Sai Manikanta</t>
         </is>
       </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>Information Technology Specialist Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="C395" s="10" t="inlineStr">
@@ -11581,6 +13516,11 @@
           <t>Riyan Imtiyaz</t>
         </is>
       </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="C396" s="10" t="inlineStr">
@@ -11609,6 +13549,11 @@
           <t>Shardul Malhotra</t>
         </is>
       </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="C397" s="10" t="inlineStr">
@@ -11637,6 +13582,11 @@
           <t>Shashwat Yadav</t>
         </is>
       </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="C398" s="10" t="inlineStr">
@@ -11665,6 +13615,11 @@
           <t>Pritpal Singh</t>
         </is>
       </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="C399" s="10" t="inlineStr">
@@ -11693,6 +13648,11 @@
           <t>Venkata Satya Sai Bokka</t>
         </is>
       </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>Information Technology Specialist Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="C400" s="10" t="inlineStr">
@@ -11721,6 +13681,11 @@
           <t>Khushi Saini</t>
         </is>
       </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="C401" s="10" t="inlineStr">
@@ -11749,6 +13714,11 @@
           <t>Damarla Jaswanth Naga Sai Venkat</t>
         </is>
       </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="C402" s="10" t="inlineStr">
@@ -11777,6 +13747,11 @@
           <t>Yasha Tasaneem</t>
         </is>
       </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="C403" s="10" t="inlineStr">
@@ -11805,6 +13780,11 @@
           <t>Piyush Sharma</t>
         </is>
       </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>Microsoft certifications</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="C404" s="10" t="inlineStr">
@@ -11833,6 +13813,11 @@
           <t>Chitjeet Singh Shahid</t>
         </is>
       </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="C405" s="10" t="inlineStr">
@@ -11861,6 +13846,11 @@
           <t>Simar</t>
         </is>
       </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>Microsoft certification</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="C406" s="10" t="inlineStr">
@@ -11889,6 +13879,11 @@
           <t>Kunal Jain</t>
         </is>
       </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="C407" s="10" t="inlineStr">
@@ -11917,6 +13912,11 @@
           <t>Deval Garg</t>
         </is>
       </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>Microsoft certifications</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="C408" s="10" t="inlineStr">
@@ -11945,6 +13945,11 @@
           <t>HARMEET SINGH</t>
         </is>
       </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="C409" s="10" t="inlineStr">
@@ -11973,6 +13978,11 @@
           <t>Sanya Bhasin</t>
         </is>
       </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>Microsoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="C410" s="10" t="inlineStr">
@@ -12001,6 +14011,11 @@
           <t>Savnmandeep Kaur</t>
         </is>
       </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="C411" s="10" t="inlineStr">
@@ -12029,6 +14044,11 @@
           <t>Ramandeep Kaur</t>
         </is>
       </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="C412" s="10" t="inlineStr">
@@ -12057,6 +14077,11 @@
           <t>Rupinder Kaur</t>
         </is>
       </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="C413" s="10" t="inlineStr">
@@ -12085,6 +14110,11 @@
           <t>Parduman</t>
         </is>
       </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="C414" s="10" t="inlineStr">
@@ -12113,6 +14143,11 @@
           <t>Yuvraj Rajput</t>
         </is>
       </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>Microsoft certifications</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="C415" s="10" t="inlineStr">
@@ -12141,6 +14176,11 @@
           <t>Vishavjit singh</t>
         </is>
       </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="C416" s="10" t="inlineStr">
@@ -12169,6 +14209,11 @@
           <t>Srihitha Reddy</t>
         </is>
       </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>Microsoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="C417" s="10" t="inlineStr">
@@ -12197,6 +14242,11 @@
           <t>Souradeep Banerjee</t>
         </is>
       </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="C418" s="10" t="inlineStr">
@@ -12225,6 +14275,11 @@
           <t>ISHA</t>
         </is>
       </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>microsoft cerifications</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="C419" s="10" t="inlineStr">
@@ -12253,6 +14308,11 @@
           <t>Ashmit Singh</t>
         </is>
       </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="C420" s="10" t="inlineStr">
@@ -12281,6 +14341,11 @@
           <t>Riya Malhotra</t>
         </is>
       </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="C421" s="10" t="inlineStr">
@@ -12309,6 +14374,11 @@
           <t>VANSH KUMAR</t>
         </is>
       </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>GITHUB FOUNDATIONS</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="C422" s="10" t="inlineStr">
@@ -12337,6 +14407,11 @@
           <t>Brijesh</t>
         </is>
       </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="C423" s="10" t="inlineStr">
@@ -12365,6 +14440,11 @@
           <t>Ashish Kapoor</t>
         </is>
       </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="C424" s="10" t="inlineStr">
@@ -12393,6 +14473,11 @@
           <t>Saksham Gupta</t>
         </is>
       </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="C425" s="10" t="inlineStr">
@@ -12421,6 +14506,11 @@
           <t>Sania Joshi</t>
         </is>
       </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>Instinger</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="C426" s="10" t="inlineStr">
@@ -12449,6 +14539,11 @@
           <t>DIPTI SINHA</t>
         </is>
       </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="C427" s="10" t="inlineStr">
@@ -12477,6 +14572,11 @@
           <t>Yash Dhingra</t>
         </is>
       </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="C428" s="10" t="inlineStr">
@@ -12505,6 +14605,11 @@
           <t>Vashnavi Walia</t>
         </is>
       </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="C429" s="10" t="inlineStr">
@@ -12533,6 +14638,11 @@
           <t>Anshul Thakur</t>
         </is>
       </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>Microsoft Certified: Azure AI Fundamentals</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="C430" s="10" t="inlineStr">
@@ -12561,6 +14671,11 @@
           <t>Prathana Kalai</t>
         </is>
       </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="C431" s="10" t="inlineStr">
@@ -12589,6 +14704,11 @@
           <t>Akkinapalli Srinivas</t>
         </is>
       </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>Microsoft Azure Fundamentals</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="C432" s="10" t="inlineStr">
@@ -12617,6 +14737,11 @@
           <t>Tanmay Yadav</t>
         </is>
       </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="C433" s="10" t="inlineStr">
@@ -12645,6 +14770,11 @@
           <t>Jatin</t>
         </is>
       </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>Fortinet</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="C434" s="10" t="inlineStr">
@@ -12673,6 +14803,11 @@
           <t>Bhumi Kapoor</t>
         </is>
       </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>Github</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="C435" s="10" t="inlineStr">
@@ -12701,6 +14836,11 @@
           <t>Yashika Yadav</t>
         </is>
       </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>Information technology in data analytics</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="C436" s="10" t="inlineStr">
@@ -12729,6 +14869,11 @@
           <t>Aastha</t>
         </is>
       </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="C437" s="10" t="inlineStr">
@@ -12757,6 +14902,11 @@
           <t>Harsh Partap Jain</t>
         </is>
       </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>Microsoft Certified</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="C438" s="10" t="inlineStr">
@@ -12785,6 +14935,11 @@
           <t>Garikapati Abhiram</t>
         </is>
       </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="C439" s="10" t="inlineStr">
@@ -12813,6 +14968,11 @@
           <t>Aamir Ekbal</t>
         </is>
       </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="C440" s="10" t="inlineStr">
@@ -12841,6 +15001,11 @@
           <t>Khavind Chaudhary</t>
         </is>
       </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>Microsoft certifications</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="C441" s="10" t="inlineStr">
@@ -12869,6 +15034,11 @@
           <t>Jyoti</t>
         </is>
       </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="C442" s="10" t="inlineStr">
@@ -12897,6 +15067,11 @@
           <t>Swyam</t>
         </is>
       </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="C443" s="10" t="inlineStr">
@@ -12925,6 +15100,11 @@
           <t>Devansh Sharma</t>
         </is>
       </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="C444" s="10" t="inlineStr">
@@ -12953,6 +15133,11 @@
           <t>Shamanyu Kashyap</t>
         </is>
       </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>Backend: Python + Flask  • Frontend: HTML, CSS  • Visualization: Matplotlib/Chart.js  • Database: SQLite for logging</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="C445" s="10" t="inlineStr">
@@ -12981,6 +15166,11 @@
           <t>Deepanshu</t>
         </is>
       </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>Microsoft Certified: Azure AI Fundamentals</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="C446" s="10" t="inlineStr">
@@ -13009,6 +15199,11 @@
           <t>srish tiwari</t>
         </is>
       </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>pearson</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="C447" s="10" t="inlineStr">
@@ -13037,6 +15232,11 @@
           <t>Shreyas Gautam</t>
         </is>
       </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="C448" s="10" t="inlineStr">
@@ -13065,6 +15265,11 @@
           <t>Gurleen Kaur</t>
         </is>
       </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="C449" s="10" t="inlineStr">
@@ -13093,6 +15298,11 @@
           <t>Manya</t>
         </is>
       </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="C450" s="10" t="inlineStr">
@@ -13121,6 +15331,11 @@
           <t>NUTAN PHADTARE</t>
         </is>
       </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="C451" s="10" t="inlineStr">
@@ -13149,6 +15364,11 @@
           <t>Aditya Kumar</t>
         </is>
       </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="C452" s="10" t="inlineStr">
@@ -13177,6 +15397,11 @@
           <t>Abhishek jain</t>
         </is>
       </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>Bitrox</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="C453" s="10" t="inlineStr">
@@ -13205,6 +15430,11 @@
           <t>Shivani Choudhary</t>
         </is>
       </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>Microsoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="C454" s="10" t="inlineStr">
@@ -13233,6 +15463,11 @@
           <t>Jatin Dhull</t>
         </is>
       </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="C455" s="10" t="inlineStr">
@@ -13261,6 +15496,11 @@
           <t>Soumyadip</t>
         </is>
       </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="C456" s="10" t="inlineStr">
@@ -13289,6 +15529,11 @@
           <t>Abhishek Thakur</t>
         </is>
       </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="C457" s="10" t="inlineStr">
@@ -13317,6 +15562,11 @@
           <t>SHAIK ANAS</t>
         </is>
       </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="C458" s="10" t="inlineStr">
@@ -13345,6 +15595,11 @@
           <t>Anvesha</t>
         </is>
       </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="C459" s="10" t="inlineStr">
@@ -13373,6 +15628,11 @@
           <t>Balaji A</t>
         </is>
       </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="C460" s="10" t="inlineStr">
@@ -13401,6 +15661,11 @@
           <t>Om Prakash Yadav</t>
         </is>
       </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="C461" s="10" t="inlineStr">
@@ -13429,6 +15694,11 @@
           <t>K Nikhil Nowshan</t>
         </is>
       </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="C462" s="10" t="inlineStr">
@@ -13457,6 +15727,11 @@
           <t>Chimbili Sreekar</t>
         </is>
       </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="C463" s="10" t="inlineStr">
@@ -13485,6 +15760,11 @@
           <t>Vivaan</t>
         </is>
       </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="C464" s="10" t="inlineStr">
@@ -13513,6 +15793,11 @@
           <t>Kaushik Bhadra</t>
         </is>
       </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="C465" s="10" t="inlineStr">
@@ -13541,6 +15826,11 @@
           <t>Priyanshi</t>
         </is>
       </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>GMETRIX</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="C466" s="10" t="inlineStr">
@@ -13569,6 +15859,11 @@
           <t>Tina khatri</t>
         </is>
       </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="C467" s="10" t="inlineStr">
@@ -13597,6 +15892,11 @@
           <t>Madhusnigdha Dash</t>
         </is>
       </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>Microsoft certification</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="C468" s="10" t="inlineStr">
@@ -13625,6 +15925,11 @@
           <t>Manya</t>
         </is>
       </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="C469" s="10" t="inlineStr">
@@ -13653,6 +15958,11 @@
           <t>KRISH KATHURIA</t>
         </is>
       </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="C470" s="10" t="inlineStr">
@@ -13681,6 +15991,11 @@
           <t>Inderpreet Singh</t>
         </is>
       </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="C471" s="10" t="inlineStr">
@@ -13709,6 +16024,11 @@
           <t>Vikranth Keshav</t>
         </is>
       </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="C472" s="10" t="inlineStr">
@@ -13737,6 +16057,11 @@
           <t>Manya</t>
         </is>
       </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="C473" s="10" t="inlineStr">
@@ -13765,6 +16090,11 @@
           <t>Ankur Sharma</t>
         </is>
       </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>EDIGLOBE</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="C474" s="10" t="inlineStr">
@@ -13793,6 +16123,11 @@
           <t>Anuj Singh</t>
         </is>
       </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="C475" s="10" t="inlineStr">
@@ -13821,6 +16156,11 @@
           <t>Prince</t>
         </is>
       </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="C476" s="10" t="inlineStr">
@@ -13849,6 +16189,11 @@
           <t>Vanshika</t>
         </is>
       </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>In-house summer training</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="C477" s="10" t="inlineStr">
@@ -13877,6 +16222,11 @@
           <t>Rishit Sagar</t>
         </is>
       </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="C478" s="10" t="inlineStr">
@@ -13905,6 +16255,11 @@
           <t>Sakshi Kumari</t>
         </is>
       </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="C479" s="10" t="inlineStr">
@@ -13933,6 +16288,11 @@
           <t>Ayush Sinha</t>
         </is>
       </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="C480" s="10" t="inlineStr">
@@ -13961,6 +16321,11 @@
           <t>Anannya</t>
         </is>
       </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="C481" s="10" t="inlineStr">
@@ -13989,6 +16354,11 @@
           <t>Harshita</t>
         </is>
       </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>Github Foundation</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="C482" s="10" t="inlineStr">
@@ -14017,6 +16387,11 @@
           <t>Dhanyasai Supraja</t>
         </is>
       </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="C483" s="10" t="inlineStr">
@@ -14045,6 +16420,11 @@
           <t>Sharath</t>
         </is>
       </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>microsoft azure</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="C484" s="10" t="inlineStr">
@@ -14073,6 +16453,11 @@
           <t>Nutan Phadtare</t>
         </is>
       </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="C485" s="10" t="inlineStr">
@@ -14101,6 +16486,11 @@
           <t>Asmita Singh</t>
         </is>
       </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="C486" s="10" t="inlineStr">
@@ -14129,6 +16519,11 @@
           <t>Manya</t>
         </is>
       </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="C487" s="10" t="inlineStr">
@@ -14157,6 +16552,11 @@
           <t>Mohammad Mehfooz</t>
         </is>
       </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>Fortinet</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="C488" s="10" t="inlineStr">
@@ -14185,6 +16585,11 @@
           <t>Aryan Koundal</t>
         </is>
       </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>Fortinet</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="C489" s="10" t="inlineStr">
@@ -14213,6 +16618,11 @@
           <t>Paras Sharma</t>
         </is>
       </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>EdiGlobe Pvt. Ltd.</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="C490" s="10" t="inlineStr">
@@ -14241,6 +16651,11 @@
           <t>Manjot Singh Randhawa</t>
         </is>
       </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>In-house summer training</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="C491" s="10" t="inlineStr">
@@ -14269,6 +16684,11 @@
           <t>Sparsh Sahni</t>
         </is>
       </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="C492" s="10" t="inlineStr">
@@ -14297,6 +16717,11 @@
           <t>Manpreet Singh</t>
         </is>
       </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="C493" s="10" t="inlineStr">
@@ -14325,6 +16750,11 @@
           <t>Priyal Sabharwal</t>
         </is>
       </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>Cisco Networking Academy</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="C494" s="10" t="inlineStr">
@@ -14353,6 +16783,11 @@
           <t>Manvi</t>
         </is>
       </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="C495" s="10" t="inlineStr">
@@ -14381,6 +16816,11 @@
           <t>FATHIMATHU RUSFIDA</t>
         </is>
       </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="C496" s="10" t="inlineStr">
@@ -14409,6 +16849,11 @@
           <t>Adithyaraj</t>
         </is>
       </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="C497" s="10" t="inlineStr">
@@ -14437,6 +16882,11 @@
           <t>Aashi Sharma</t>
         </is>
       </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>Certiport , Certnexus ,Pearson</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="C498" s="10" t="inlineStr">
@@ -14465,6 +16915,11 @@
           <t>Gaurav Sood</t>
         </is>
       </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="C499" s="10" t="inlineStr">
@@ -14493,6 +16948,11 @@
           <t>Yeddula Pavan Tejeswar Reddy</t>
         </is>
       </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>FORTINET</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="C500" s="10" t="inlineStr">
@@ -14521,6 +16981,11 @@
           <t>Sikander</t>
         </is>
       </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>CHANDIGARH UNIVERSITY</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="C501" s="10" t="inlineStr">
@@ -14549,6 +17014,11 @@
           <t>Aastha wadhwa</t>
         </is>
       </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>Microsoft certifications</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="C502" s="10" t="inlineStr">
@@ -14577,6 +17047,11 @@
           <t>Priyal</t>
         </is>
       </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>Cisco Networking Academy</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="C503" s="10" t="inlineStr">
@@ -14605,6 +17080,11 @@
           <t>lavish</t>
         </is>
       </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="C504" s="10" t="inlineStr">
@@ -14633,6 +17113,11 @@
           <t>Priyanshu Yadav</t>
         </is>
       </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="C505" s="10" t="inlineStr">
@@ -14661,6 +17146,11 @@
           <t>Sri Manikanta</t>
         </is>
       </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="C506" s="10" t="inlineStr">
@@ -14689,6 +17179,11 @@
           <t>Devansh Tyagi</t>
         </is>
       </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>Fortinet</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="C507" s="10" t="inlineStr">
@@ -14717,6 +17212,11 @@
           <t>Priyanshi</t>
         </is>
       </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>GMETRIX</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="C508" s="10" t="inlineStr">
@@ -14745,6 +17245,11 @@
           <t>Navneet kaur</t>
         </is>
       </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="C509" s="10" t="inlineStr">
@@ -14773,6 +17278,11 @@
           <t>Adarsh Deep</t>
         </is>
       </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="C510" s="10" t="inlineStr">
@@ -14801,6 +17311,11 @@
           <t>Anantpreet Singh Dhaliwal</t>
         </is>
       </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="C511" s="10" t="inlineStr">
@@ -14829,6 +17344,11 @@
           <t>Dheeraj Kumar</t>
         </is>
       </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>SalesForce</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="C512" s="10" t="inlineStr">
@@ -14857,6 +17377,11 @@
           <t>PARV DHAREULA</t>
         </is>
       </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>Ai azure Fundamentals</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="C513" s="10" t="inlineStr">
@@ -14885,6 +17410,11 @@
           <t>Vansh</t>
         </is>
       </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="C514" s="10" t="inlineStr">
@@ -14913,6 +17443,11 @@
           <t>Vansh Soin</t>
         </is>
       </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="C515" s="10" t="inlineStr">
@@ -14941,6 +17476,11 @@
           <t>harsh vardhan</t>
         </is>
       </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="C516" s="10" t="inlineStr">
@@ -14969,6 +17509,11 @@
           <t>Vansh Nandal</t>
         </is>
       </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="C517" s="10" t="inlineStr">
@@ -14997,6 +17542,11 @@
           <t>Tushar Malik</t>
         </is>
       </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="C518" s="10" t="inlineStr">
@@ -15025,6 +17575,11 @@
           <t>Kondapalli Indrani</t>
         </is>
       </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="C519" s="10" t="inlineStr">
@@ -15053,6 +17608,11 @@
           <t>23BAI70076</t>
         </is>
       </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>PEARSON INFORMATION TECHNOLOGY SPECIALIST (IT SPECIALIST) CERTIFICATION IN ARTIFICIAL INTELLIGENCE</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="C520" s="10" t="inlineStr">
@@ -15081,6 +17641,11 @@
           <t>Rishu Raj</t>
         </is>
       </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>Web Development</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="C521" s="10" t="inlineStr">
@@ -15109,6 +17674,11 @@
           <t>Shiv Gulati</t>
         </is>
       </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="C522" s="10" t="inlineStr">
@@ -15137,6 +17707,11 @@
           <t>Ashish Kumar</t>
         </is>
       </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="C523" s="10" t="inlineStr">
@@ -15165,6 +17740,11 @@
           <t>UTSHA SARKER</t>
         </is>
       </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>Dizivan IT Solutions Pvt Ltd</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="C524" s="10" t="inlineStr">
@@ -15193,6 +17773,11 @@
           <t>Archy Biswas</t>
         </is>
       </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>Dizivan IT Solutions Pvt Ltd</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="C525" s="10" t="inlineStr">
@@ -15221,6 +17806,11 @@
           <t>Animesh Saha</t>
         </is>
       </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>Adobe Express</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="C526" s="10" t="inlineStr">
@@ -15249,6 +17839,11 @@
           <t>Raja babu</t>
         </is>
       </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>Salesforce Certified</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="C527" s="10" t="inlineStr">
@@ -15277,6 +17872,11 @@
           <t>Smile Katoch</t>
         </is>
       </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="C528" s="10" t="inlineStr">
@@ -15305,6 +17905,11 @@
           <t>Akshat Pandey</t>
         </is>
       </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="C529" s="10" t="inlineStr">
@@ -15333,6 +17938,11 @@
           <t>23BAI70172</t>
         </is>
       </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="C530" s="10" t="inlineStr">
@@ -15361,6 +17971,11 @@
           <t>Gaurav Monga</t>
         </is>
       </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="C531" s="10" t="inlineStr">
@@ -15389,6 +18004,11 @@
           <t>Arnav Sharma</t>
         </is>
       </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="C532" s="10" t="inlineStr">
@@ -15417,6 +18037,11 @@
           <t>Lesham Rai</t>
         </is>
       </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="C533" s="10" t="inlineStr">
@@ -15445,6 +18070,11 @@
           <t>Aishna Goyal</t>
         </is>
       </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="C534" s="10" t="inlineStr">
@@ -15473,6 +18103,11 @@
           <t>Jagdeep Singh</t>
         </is>
       </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="C535" s="10" t="inlineStr">
@@ -15501,6 +18136,11 @@
           <t>Saptangshu Saha</t>
         </is>
       </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="C536" s="10" t="inlineStr">
@@ -15529,6 +18169,11 @@
           <t>Lesham Rai</t>
         </is>
       </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="C537" s="10" t="inlineStr">
@@ -15557,6 +18202,11 @@
           <t>Setti Hari krishna</t>
         </is>
       </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>PrernaGati &amp; technologies</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="C538" s="10" t="inlineStr">
@@ -15585,6 +18235,11 @@
           <t>Ridhima</t>
         </is>
       </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>Microsoft certification</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="C539" s="10" t="inlineStr">
@@ -15613,6 +18268,11 @@
           <t>Yasha Tasaneem</t>
         </is>
       </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="C540" s="10" t="inlineStr">
@@ -15641,6 +18301,11 @@
           <t>UDAY SHARMA</t>
         </is>
       </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="C541" s="10" t="inlineStr">
@@ -15669,6 +18334,11 @@
           <t>Dev chaurasia</t>
         </is>
       </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>PLASMID ( MSME )</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="C542" s="10" t="inlineStr">
@@ -15697,6 +18367,11 @@
           <t>Rishika jagota</t>
         </is>
       </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
     </row>
     <row r="543">
       <c r="C543" s="10" t="inlineStr">
@@ -15725,6 +18400,11 @@
           <t>Sujal Goyal</t>
         </is>
       </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>Microsoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="C544" s="10" t="inlineStr">
@@ -15753,6 +18433,11 @@
           <t>Vikash</t>
         </is>
       </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>Unity Technology</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="C545" s="10" t="inlineStr">
@@ -15781,6 +18466,11 @@
           <t>Ashmit Thakur</t>
         </is>
       </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>Salesforce {Pearson vue}</t>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="C546" s="10" t="inlineStr">
@@ -15809,6 +18499,11 @@
           <t>Tamana</t>
         </is>
       </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="C547" s="10" t="inlineStr">
@@ -15837,6 +18532,11 @@
           <t>mohit kumar</t>
         </is>
       </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="C548" s="10" t="inlineStr">
@@ -15865,6 +18565,11 @@
           <t>Arnav Saini</t>
         </is>
       </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>The forage</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="C549" s="10" t="inlineStr">
@@ -15893,6 +18598,11 @@
           <t>Aniket Sharma</t>
         </is>
       </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="C550" s="10" t="inlineStr">
@@ -15921,6 +18631,11 @@
           <t>Anvi</t>
         </is>
       </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="C551" s="10" t="inlineStr">
@@ -15949,6 +18664,11 @@
           <t>Deepanshu Yadav</t>
         </is>
       </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="C552" s="10" t="inlineStr">
@@ -15977,6 +18697,11 @@
           <t>Shubhshri Rajvansh</t>
         </is>
       </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="C553" s="10" t="inlineStr">
@@ -16005,6 +18730,11 @@
           <t>Kasam Vivek Reddy</t>
         </is>
       </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>Microsoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="554">
       <c r="C554" s="10" t="inlineStr">
@@ -16033,6 +18763,11 @@
           <t>Vansh Sharma</t>
         </is>
       </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="C555" s="10" t="inlineStr">
@@ -16061,6 +18796,11 @@
           <t>YASH RAJ YADAV</t>
         </is>
       </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="556">
       <c r="C556" s="10" t="inlineStr">
@@ -16089,6 +18829,11 @@
           <t>Ishwar Dagar</t>
         </is>
       </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="C557" s="10" t="inlineStr">
@@ -16117,6 +18862,11 @@
           <t>Kavita Bathyal</t>
         </is>
       </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="C558" s="10" t="inlineStr">
@@ -16145,6 +18895,11 @@
           <t>Prabhleen Nagi</t>
         </is>
       </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="C559" s="10" t="inlineStr">
@@ -16173,6 +18928,11 @@
           <t>Gagan Kumar Sharma</t>
         </is>
       </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="C560" s="10" t="inlineStr">
@@ -16201,6 +18961,11 @@
           <t>Kesab Agarwal</t>
         </is>
       </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>FORTINET</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="C561" s="10" t="inlineStr">
@@ -16229,6 +18994,11 @@
           <t>Priyanshu Sharma</t>
         </is>
       </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="562">
       <c r="C562" s="10" t="inlineStr">
@@ -16257,6 +19027,11 @@
           <t>Harsh Bardhan Singh</t>
         </is>
       </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>Microsoft Cerification</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="C563" s="10" t="inlineStr">
@@ -16285,6 +19060,11 @@
           <t>Arushi</t>
         </is>
       </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="C564" s="10" t="inlineStr">
@@ -16313,6 +19093,11 @@
           <t>Divyanshu Singh</t>
         </is>
       </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>GITHUB</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="C565" s="10" t="inlineStr">
@@ -16341,6 +19126,11 @@
           <t>Vinit</t>
         </is>
       </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>Dizivan IT Solutions</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="C566" s="10" t="inlineStr">
@@ -16369,6 +19159,11 @@
           <t>Mashrafee Bin sarwar</t>
         </is>
       </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>Astrit technology private limited</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="C567" s="10" t="inlineStr">
@@ -16397,6 +19192,11 @@
           <t>Gunpreet singh</t>
         </is>
       </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="C568" s="10" t="inlineStr">
@@ -16425,6 +19225,11 @@
           <t>Aditya</t>
         </is>
       </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="C569" s="10" t="inlineStr">
@@ -16453,6 +19258,11 @@
           <t>Ankush Choudhary</t>
         </is>
       </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="C570" s="10" t="inlineStr">
@@ -16481,6 +19291,11 @@
           <t>Lakshay Phogat</t>
         </is>
       </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>Trantor Software Pvt Ltd</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="C571" s="10" t="inlineStr">
@@ -16509,6 +19324,11 @@
           <t>Swansh Shree</t>
         </is>
       </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="C572" s="10" t="inlineStr">
@@ -16537,6 +19357,11 @@
           <t>Vikhyaat Dixit</t>
         </is>
       </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="573">
       <c r="C573" s="10" t="inlineStr">
@@ -16565,6 +19390,11 @@
           <t>Priyanshu Kumar</t>
         </is>
       </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="C574" s="10" t="inlineStr">
@@ -16593,6 +19423,11 @@
           <t>NAVNEET KUMAR SAINI</t>
         </is>
       </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>Microsoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="C575" s="10" t="inlineStr">
@@ -16621,6 +19456,11 @@
           <t>NEMALI MAHIVARDHANREDDY</t>
         </is>
       </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="C576" s="10" t="inlineStr">
@@ -16649,6 +19489,11 @@
           <t>charanjit singh</t>
         </is>
       </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="577">
       <c r="C577" s="10" t="inlineStr">
@@ -16677,6 +19522,11 @@
           <t>Arpit garg</t>
         </is>
       </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>Microsoft azure</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="C578" s="10" t="inlineStr">
@@ -16705,6 +19555,11 @@
           <t>Rimanshu Kakkar</t>
         </is>
       </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>Chandigarh University</t>
+        </is>
+      </c>
     </row>
     <row r="579">
       <c r="C579" s="10" t="inlineStr">
@@ -16733,6 +19588,11 @@
           <t>Divyanshu Singh</t>
         </is>
       </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>GITHUB</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="C580" s="10" t="inlineStr">
@@ -16761,6 +19621,11 @@
           <t>Tanisq</t>
         </is>
       </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>Microsoft certification</t>
+        </is>
+      </c>
     </row>
     <row r="581">
       <c r="C581" s="10" t="inlineStr">
@@ -16789,6 +19654,11 @@
           <t>Ashlin James Chakkalakkal</t>
         </is>
       </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="582">
       <c r="C582" s="10" t="inlineStr">
@@ -16817,6 +19687,11 @@
           <t>Naveen</t>
         </is>
       </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
     </row>
     <row r="583">
       <c r="C583" s="10" t="inlineStr">
@@ -16845,6 +19720,11 @@
           <t>Adarsh Kumar</t>
         </is>
       </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="584">
       <c r="C584" s="10" t="inlineStr">
@@ -16873,6 +19753,11 @@
           <t>Arpeet Kandhol</t>
         </is>
       </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="C585" s="10" t="inlineStr">
@@ -16901,6 +19786,11 @@
           <t>Gursharan singh</t>
         </is>
       </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>Inhouse training</t>
+        </is>
+      </c>
     </row>
     <row r="586">
       <c r="C586" s="10" t="inlineStr">
@@ -16929,6 +19819,11 @@
           <t>Priyanshu Agarwal</t>
         </is>
       </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
     </row>
     <row r="587">
       <c r="C587" s="10" t="inlineStr">
@@ -16957,6 +19852,11 @@
           <t>Vishwas mohan sharma</t>
         </is>
       </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>Miscrosoft</t>
+        </is>
+      </c>
     </row>
     <row r="588">
       <c r="C588" s="10" t="inlineStr">
@@ -16985,6 +19885,11 @@
           <t>Ankush Choudhary</t>
         </is>
       </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="C589" s="10" t="inlineStr">
@@ -17013,6 +19918,11 @@
           <t>ADITHYAN M B</t>
         </is>
       </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="C590" s="10" t="inlineStr">
@@ -17041,6 +19951,11 @@
           <t>Saurabh</t>
         </is>
       </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>GitHub Foundations</t>
+        </is>
+      </c>
     </row>
     <row r="591">
       <c r="C591" s="10" t="inlineStr">
@@ -17069,6 +19984,11 @@
           <t>Rishav Pal</t>
         </is>
       </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>Full Stack Development</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="C592" s="10" t="inlineStr">
@@ -17097,6 +20017,11 @@
           <t>Gautam Dhiman</t>
         </is>
       </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="593">
       <c r="C593" s="10" t="inlineStr">
@@ -17125,6 +20050,11 @@
           <t>Deepansh Kainth</t>
         </is>
       </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
     </row>
     <row r="594">
       <c r="C594" s="10" t="inlineStr">
@@ -17153,6 +20083,11 @@
           <t>Jitesh</t>
         </is>
       </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>Microsoft certified: Azure AI Fundamentals</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="C595" s="10" t="inlineStr">
@@ -17181,6 +20116,11 @@
           <t>Anshveer Thakur</t>
         </is>
       </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>XpressBites technology</t>
+        </is>
+      </c>
     </row>
     <row r="596">
       <c r="C596" s="10" t="inlineStr">
@@ -17209,6 +20149,11 @@
           <t>Shubham Sharma</t>
         </is>
       </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="597">
       <c r="C597" s="10" t="inlineStr">
@@ -17237,6 +20182,11 @@
           <t>Animesh Yadav</t>
         </is>
       </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>INFOWAY</t>
+        </is>
+      </c>
     </row>
     <row r="598">
       <c r="C598" s="10" t="inlineStr">
@@ -17265,6 +20215,11 @@
           <t>Donuru Siddharth Reddy</t>
         </is>
       </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>Fortinet training institute</t>
+        </is>
+      </c>
     </row>
     <row r="599">
       <c r="C599" s="10" t="inlineStr">
@@ -17293,6 +20248,11 @@
           <t>Pabolu Syama Satya Sri Phani Pradeep</t>
         </is>
       </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="600">
       <c r="C600" s="10" t="inlineStr">
@@ -17321,6 +20281,11 @@
           <t>Abhinav</t>
         </is>
       </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>Project Management Institute</t>
+        </is>
+      </c>
     </row>
     <row r="601">
       <c r="C601" s="10" t="inlineStr">
@@ -17349,6 +20314,11 @@
           <t>Naveen</t>
         </is>
       </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
     </row>
     <row r="602">
       <c r="C602" s="10" t="inlineStr">
@@ -17377,6 +20347,11 @@
           <t>Rohit Yadav</t>
         </is>
       </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="603">
       <c r="C603" s="10" t="inlineStr">
@@ -17405,6 +20380,11 @@
           <t>Preeti shah</t>
         </is>
       </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>pearson</t>
+        </is>
+      </c>
     </row>
     <row r="604">
       <c r="C604" s="10" t="inlineStr">
@@ -17433,6 +20413,11 @@
           <t>mannat</t>
         </is>
       </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>microsoft certification</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="C605" s="10" t="inlineStr">
@@ -17461,6 +20446,11 @@
           <t>Akshay Thakur</t>
         </is>
       </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
     </row>
     <row r="606">
       <c r="C606" s="10" t="inlineStr">
@@ -17489,6 +20479,11 @@
           <t>B.OMPRAKASH REDDY</t>
         </is>
       </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="607">
       <c r="C607" s="10" t="inlineStr">
@@ -17517,6 +20512,11 @@
           <t>Ashutosh Saini</t>
         </is>
       </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>Unity</t>
+        </is>
+      </c>
     </row>
     <row r="608">
       <c r="C608" s="10" t="inlineStr">
@@ -17545,6 +20545,11 @@
           <t>Palash Mathur</t>
         </is>
       </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>Apple Inc &amp; Certiport</t>
+        </is>
+      </c>
     </row>
     <row r="609">
       <c r="C609" s="10" t="inlineStr">
@@ -17573,6 +20578,11 @@
           <t>MANPREET SINGH</t>
         </is>
       </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="610">
       <c r="C610" s="10" t="inlineStr">
@@ -17601,6 +20611,11 @@
           <t>Nishant Sharma</t>
         </is>
       </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>Xpress Bites</t>
+        </is>
+      </c>
     </row>
     <row r="611">
       <c r="C611" s="10" t="inlineStr">
@@ -17629,6 +20644,11 @@
           <t>Priyanshu Yadav</t>
         </is>
       </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="612">
       <c r="C612" s="10" t="inlineStr">
@@ -17657,6 +20677,11 @@
           <t>Rudransh Agarwal</t>
         </is>
       </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="613">
       <c r="C613" s="10" t="inlineStr">
@@ -17685,6 +20710,11 @@
           <t>sanat singh</t>
         </is>
       </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>Fortinet Training Institute</t>
+        </is>
+      </c>
     </row>
     <row r="614">
       <c r="C614" s="10" t="inlineStr">
@@ -17713,6 +20743,11 @@
           <t>Priyansh Mangesh Kale</t>
         </is>
       </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="615">
       <c r="C615" s="10" t="inlineStr">
@@ -17741,6 +20776,11 @@
           <t>Mayank Singla</t>
         </is>
       </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>Certiport</t>
+        </is>
+      </c>
     </row>
     <row r="616">
       <c r="C616" s="10" t="inlineStr">
@@ -17769,6 +20809,11 @@
           <t>Ashmit Thakur</t>
         </is>
       </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>Salesforce {Pearson vue}</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="C617" s="10" t="inlineStr">
@@ -17797,6 +20842,11 @@
           <t>Akshat Pandey</t>
         </is>
       </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
     </row>
     <row r="618">
       <c r="C618" s="10" t="inlineStr">
@@ -17825,6 +20875,11 @@
           <t>arpit garg</t>
         </is>
       </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>Microsoft azure</t>
+        </is>
+      </c>
     </row>
     <row r="619">
       <c r="C619" s="10" t="inlineStr">
@@ -17853,6 +20908,11 @@
           <t>Prashant</t>
         </is>
       </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>SALESFORCE</t>
+        </is>
+      </c>
     </row>
     <row r="620">
       <c r="C620" s="10" t="inlineStr">
@@ -17881,6 +20941,11 @@
           <t>Vanshdeep</t>
         </is>
       </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
     </row>
     <row r="621">
       <c r="C621" s="10" t="inlineStr">
@@ -17909,6 +20974,11 @@
           <t>Japkirat Kaur</t>
         </is>
       </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="622">
       <c r="C622" s="10" t="inlineStr">
@@ -17937,6 +21007,11 @@
           <t>Deepjoy Paul</t>
         </is>
       </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>pearson</t>
+        </is>
+      </c>
     </row>
     <row r="623">
       <c r="C623" s="10" t="inlineStr">
@@ -17965,6 +21040,11 @@
           <t>Hardik</t>
         </is>
       </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="624">
       <c r="C624" s="10" t="inlineStr">
@@ -17993,6 +21073,11 @@
           <t>Akshpreet Singh</t>
         </is>
       </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>microsoft and github</t>
+        </is>
+      </c>
     </row>
     <row r="625">
       <c r="C625" s="10" t="inlineStr">
@@ -18021,6 +21106,11 @@
           <t>Saptangshu Saha</t>
         </is>
       </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="626">
       <c r="C626" s="10" t="inlineStr">
@@ -18049,6 +21139,11 @@
           <t>Atharv Sharma</t>
         </is>
       </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
     </row>
     <row r="627">
       <c r="C627" s="10" t="inlineStr">
@@ -18077,6 +21172,11 @@
           <t>RISHI JAIN</t>
         </is>
       </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="628">
       <c r="C628" s="10" t="inlineStr">
@@ -18105,6 +21205,11 @@
           <t>TANISHA SINGH</t>
         </is>
       </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
     </row>
     <row r="629">
       <c r="C629" s="10" t="inlineStr">
@@ -18133,6 +21238,11 @@
           <t>Shivom Parashari</t>
         </is>
       </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="630">
       <c r="C630" s="10" t="inlineStr">
@@ -18161,6 +21271,11 @@
           <t>Shamanyu Kashyap</t>
         </is>
       </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>Backend: Python + Flask  • Frontend: HTML, CSS  • Visualization: Matplotlib/Chart.js  • Database: SQLite for logging</t>
+        </is>
+      </c>
     </row>
     <row r="631">
       <c r="C631" s="10" t="inlineStr">
@@ -18189,6 +21304,11 @@
           <t>Aakrisht Banyal</t>
         </is>
       </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="632">
       <c r="C632" s="10" t="inlineStr">
@@ -18217,6 +21337,11 @@
           <t>Sunidhi Chauhan</t>
         </is>
       </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>EC Council</t>
+        </is>
+      </c>
     </row>
     <row r="633">
       <c r="C633" s="10" t="inlineStr">
@@ -18245,6 +21370,11 @@
           <t>Sukhjinder Singh</t>
         </is>
       </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="634">
       <c r="C634" s="10" t="inlineStr">
@@ -18273,6 +21403,11 @@
           <t>Paras</t>
         </is>
       </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="635">
       <c r="C635" s="10" t="inlineStr">
@@ -18301,6 +21436,11 @@
           <t>Tushar Malik</t>
         </is>
       </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="636">
       <c r="C636" s="10" t="inlineStr">
@@ -18329,6 +21469,11 @@
           <t>Tusar Rana</t>
         </is>
       </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>Xpressbites</t>
+        </is>
+      </c>
     </row>
     <row r="637">
       <c r="C637" s="10" t="inlineStr">
@@ -18357,6 +21502,11 @@
           <t>Anuj Sharma</t>
         </is>
       </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>Microsoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="638">
       <c r="C638" s="10" t="inlineStr">
@@ -18385,6 +21535,11 @@
           <t>Riya Malhotra</t>
         </is>
       </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="639">
       <c r="C639" s="10" t="inlineStr">
@@ -18413,6 +21568,11 @@
           <t>Aditya Thakur</t>
         </is>
       </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
     </row>
     <row r="640">
       <c r="C640" s="10" t="inlineStr">
@@ -18441,6 +21601,11 @@
           <t>Janvi</t>
         </is>
       </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>XpressBites</t>
+        </is>
+      </c>
     </row>
     <row r="641">
       <c r="C641" s="10" t="inlineStr">
@@ -18469,6 +21634,11 @@
           <t>Narlakanti Vikas</t>
         </is>
       </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="642">
       <c r="C642" s="10" t="inlineStr">
@@ -18497,6 +21667,11 @@
           <t>Rajat Malik</t>
         </is>
       </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="643">
       <c r="C643" s="10" t="inlineStr">
@@ -18525,6 +21700,11 @@
           <t>kabir</t>
         </is>
       </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
     </row>
     <row r="644">
       <c r="C644" s="10" t="inlineStr">
@@ -18553,6 +21733,11 @@
           <t>Shorya Tomar</t>
         </is>
       </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="645">
       <c r="C645" s="10" t="inlineStr">
@@ -18581,6 +21766,11 @@
           <t>M.Sravani</t>
         </is>
       </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>Pearson vue</t>
+        </is>
+      </c>
     </row>
     <row r="646">
       <c r="C646" s="10" t="inlineStr">
@@ -18609,6 +21799,11 @@
           <t>Anu</t>
         </is>
       </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="647">
       <c r="C647" s="10" t="inlineStr">
@@ -18637,6 +21832,11 @@
           <t>Harinder singh</t>
         </is>
       </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
     </row>
     <row r="648">
       <c r="C648" s="10" t="inlineStr">
@@ -18665,6 +21865,11 @@
           <t>Riya Kashyap</t>
         </is>
       </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>Microsoft certifications</t>
+        </is>
+      </c>
     </row>
     <row r="649">
       <c r="C649" s="10" t="inlineStr">
@@ -18693,6 +21898,11 @@
           <t>Gaurav kadyan</t>
         </is>
       </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="650">
       <c r="C650" s="10" t="inlineStr">
@@ -18721,6 +21931,11 @@
           <t>Rishika jagota</t>
         </is>
       </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
     </row>
     <row r="651">
       <c r="C651" s="10" t="inlineStr">
@@ -18749,6 +21964,11 @@
           <t>Sakshamm Khanna</t>
         </is>
       </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
     </row>
     <row r="652">
       <c r="C652" s="10" t="inlineStr">
@@ -18777,6 +21997,11 @@
           <t>Shivani Thakur</t>
         </is>
       </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="653">
       <c r="C653" s="10" t="inlineStr">
@@ -18805,6 +22030,11 @@
           <t>Divyansh</t>
         </is>
       </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>Github</t>
+        </is>
+      </c>
     </row>
     <row r="654">
       <c r="C654" s="10" t="inlineStr">
@@ -18833,6 +22063,11 @@
           <t>Tiksha Gupta</t>
         </is>
       </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
     </row>
     <row r="655">
       <c r="C655" s="10" t="inlineStr">
@@ -18861,6 +22096,11 @@
           <t>kabir</t>
         </is>
       </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
     </row>
     <row r="656">
       <c r="C656" s="10" t="inlineStr">
@@ -18889,6 +22129,11 @@
           <t>Dheeraj VP</t>
         </is>
       </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="657">
       <c r="C657" s="10" t="inlineStr">
@@ -18917,6 +22162,11 @@
           <t>S S Sneha</t>
         </is>
       </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>Microsoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="658">
       <c r="C658" s="10" t="inlineStr">
@@ -18945,6 +22195,11 @@
           <t>MD AL EMRAN</t>
         </is>
       </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>Github</t>
+        </is>
+      </c>
     </row>
     <row r="659">
       <c r="C659" s="10" t="inlineStr">
@@ -18973,6 +22228,11 @@
           <t>Vansh Tripathi</t>
         </is>
       </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>information technology specialist</t>
+        </is>
+      </c>
     </row>
     <row r="660">
       <c r="C660" s="10" t="inlineStr">
@@ -19001,6 +22261,11 @@
           <t>OM PRAKASH YADAV</t>
         </is>
       </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
     </row>
     <row r="661">
       <c r="C661" s="10" t="inlineStr">
@@ -19029,6 +22294,11 @@
           <t>Mahesh Kumar</t>
         </is>
       </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="662">
       <c r="C662" s="10" t="inlineStr">
@@ -19057,6 +22327,11 @@
           <t>VIVEK YADAV</t>
         </is>
       </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
     </row>
     <row r="663">
       <c r="C663" s="10" t="inlineStr">
@@ -19085,6 +22360,11 @@
           <t>Harjasjot Singh Sidhu</t>
         </is>
       </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="664">
       <c r="C664" s="10" t="inlineStr">
@@ -19113,6 +22393,11 @@
           <t>Shivansh Kutlehria</t>
         </is>
       </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>microsoft certifications</t>
+        </is>
+      </c>
     </row>
     <row r="665">
       <c r="C665" s="10" t="inlineStr">
@@ -19141,6 +22426,11 @@
           <t>Aaditya</t>
         </is>
       </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
     </row>
     <row r="666">
       <c r="C666" s="10" t="inlineStr">
@@ -19169,6 +22459,11 @@
           <t>Himanshu</t>
         </is>
       </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>SDE Intern in Full Stack</t>
+        </is>
+      </c>
     </row>
     <row r="667">
       <c r="C667" s="10" t="inlineStr">
@@ -19197,6 +22492,11 @@
           <t>Sulaksh Kharal</t>
         </is>
       </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>Dizivan IT Solutions Pvt Ltd</t>
+        </is>
+      </c>
     </row>
     <row r="668">
       <c r="C668" s="10" t="inlineStr">
@@ -19225,6 +22525,11 @@
           <t>Ramik chauhan</t>
         </is>
       </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>microsoft azure</t>
+        </is>
+      </c>
     </row>
     <row r="669">
       <c r="C669" s="10" t="inlineStr">
@@ -19253,6 +22558,11 @@
           <t>Harshdeep Singh</t>
         </is>
       </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
     </row>
     <row r="670">
       <c r="C670" s="10" t="inlineStr">
@@ -19281,6 +22591,11 @@
           <t>UTSHA SARKER</t>
         </is>
       </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>Dizivan IT Solutions Pvt Ltd</t>
+        </is>
+      </c>
     </row>
     <row r="671">
       <c r="C671" s="10" t="inlineStr">
@@ -19309,6 +22624,11 @@
           <t>Mohit kumar</t>
         </is>
       </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="672">
       <c r="C672" s="10" t="inlineStr">
@@ -19337,6 +22657,11 @@
           <t>Lesham Rai</t>
         </is>
       </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="673">
       <c r="C673" s="10" t="inlineStr">
@@ -19365,6 +22690,11 @@
           <t>Sukhmanpreet Singh</t>
         </is>
       </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>Microsoft Certifification</t>
+        </is>
+      </c>
     </row>
     <row r="674">
       <c r="C674" s="10" t="inlineStr">
@@ -19393,6 +22723,11 @@
           <t>Shivam Sharma</t>
         </is>
       </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>Microsoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="675">
       <c r="C675" s="10" t="inlineStr">
@@ -19421,6 +22756,11 @@
           <t>Madhav</t>
         </is>
       </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>Meander Software  Pvt. Ltd.</t>
+        </is>
+      </c>
     </row>
     <row r="676">
       <c r="C676" s="10" t="inlineStr">
@@ -19449,6 +22789,11 @@
           <t>ARCHY BISWAS</t>
         </is>
       </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>Dizivan IT Solutions Pvt Ltd</t>
+        </is>
+      </c>
     </row>
     <row r="677">
       <c r="C677" s="10" t="inlineStr">
@@ -19477,6 +22822,11 @@
           <t>Charanjit Singh</t>
         </is>
       </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="678">
       <c r="C678" s="10" t="inlineStr">
@@ -19505,6 +22855,11 @@
           <t>Gursimran Singh</t>
         </is>
       </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="679">
       <c r="C679" s="10" t="inlineStr">
@@ -19533,6 +22888,11 @@
           <t>Prosenjit Debnath</t>
         </is>
       </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>Dizivan IT Solutions</t>
+        </is>
+      </c>
     </row>
     <row r="680">
       <c r="C680" s="10" t="inlineStr">
@@ -19561,6 +22921,11 @@
           <t>Atul Kumar</t>
         </is>
       </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="681">
       <c r="C681" s="10" t="inlineStr">
@@ -19589,6 +22954,11 @@
           <t>Agastya Vashisht</t>
         </is>
       </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="682">
       <c r="C682" s="10" t="inlineStr">
@@ -19617,6 +22987,11 @@
           <t>Anshika Sinha</t>
         </is>
       </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="683">
       <c r="C683" s="10" t="inlineStr">
@@ -19645,6 +23020,11 @@
           <t>Ayush Kumar</t>
         </is>
       </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="684">
       <c r="C684" s="10" t="inlineStr">
@@ -19673,6 +23053,11 @@
           <t>Vansh Tripathi</t>
         </is>
       </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>information technology specialist</t>
+        </is>
+      </c>
     </row>
     <row r="685">
       <c r="C685" s="10" t="inlineStr">
@@ -19701,6 +23086,11 @@
           <t>Aakrisht Banyal</t>
         </is>
       </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="686">
       <c r="C686" s="10" t="inlineStr">
@@ -19729,6 +23119,11 @@
           <t>Shalini Kush</t>
         </is>
       </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>Issuing Authority of Professional Certification: Aptron Solutions Pvt. Ltd., Gurgaon</t>
+        </is>
+      </c>
     </row>
     <row r="687">
       <c r="C687" s="10" t="inlineStr">
@@ -19757,6 +23152,11 @@
           <t>Atharv Sharma</t>
         </is>
       </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
     </row>
     <row r="688">
       <c r="C688" s="10" t="inlineStr">
@@ -19785,6 +23185,11 @@
           <t>Aryan Kohli</t>
         </is>
       </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="689">
       <c r="C689" s="10" t="inlineStr">
@@ -19813,6 +23218,11 @@
           <t>Taranjot Singh</t>
         </is>
       </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="690">
       <c r="C690" s="10" t="inlineStr">
@@ -19841,6 +23251,11 @@
           <t>Harsh Raj</t>
         </is>
       </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
     </row>
     <row r="691">
       <c r="C691" s="10" t="inlineStr">
@@ -19869,6 +23284,11 @@
           <t>Jagdeep Singh</t>
         </is>
       </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="692">
       <c r="C692" s="10" t="inlineStr">
@@ -19897,6 +23317,11 @@
           <t>Tanmay Jaswal</t>
         </is>
       </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
     </row>
     <row r="693">
       <c r="C693" s="10" t="inlineStr">
@@ -19925,6 +23350,11 @@
           <t>Saneha rana</t>
         </is>
       </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>Microsoft  certificate</t>
+        </is>
+      </c>
     </row>
     <row r="694">
       <c r="C694" s="10" t="inlineStr">
@@ -19953,6 +23383,11 @@
           <t>Venkata Satya Sai Bokka</t>
         </is>
       </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>Information Technology Specialist Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="695">
       <c r="C695" s="10" t="inlineStr">
@@ -19981,6 +23416,11 @@
           <t>GURREDDY SATHYAVARDHAN REDDY</t>
         </is>
       </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>GitHub (through GitHub Education Program)</t>
+        </is>
+      </c>
     </row>
     <row r="696">
       <c r="C696" s="10" t="inlineStr">
@@ -20009,6 +23449,11 @@
           <t>Yeddula Pavan Tejeswar Reddy</t>
         </is>
       </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>FORTINET</t>
+        </is>
+      </c>
     </row>
     <row r="697">
       <c r="C697" s="10" t="inlineStr">
@@ -20037,6 +23482,11 @@
           <t>Mansi Verma</t>
         </is>
       </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="698">
       <c r="C698" s="10" t="inlineStr">
@@ -20065,6 +23515,11 @@
           <t>Asmit kumar</t>
         </is>
       </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="699">
       <c r="C699" s="10" t="inlineStr">
@@ -20093,6 +23548,11 @@
           <t>Ayush Sharma</t>
         </is>
       </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>Microsoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="700">
       <c r="C700" s="10" t="inlineStr">
@@ -20121,6 +23581,11 @@
           <t>saneha rana</t>
         </is>
       </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>Microsoft  certificate</t>
+        </is>
+      </c>
     </row>
     <row r="701">
       <c r="C701" s="10" t="inlineStr">
@@ -20149,6 +23614,11 @@
           <t>Anas Sadeq Alhamdani</t>
         </is>
       </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>Microsoft Certificate</t>
+        </is>
+      </c>
     </row>
     <row r="702">
       <c r="C702" s="10" t="inlineStr">
@@ -20177,6 +23647,11 @@
           <t>shiv raj ojha</t>
         </is>
       </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="703">
       <c r="C703" s="10" t="inlineStr">
@@ -20205,6 +23680,11 @@
           <t>Mohammed Abdul Rayaan</t>
         </is>
       </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>Dizivan IT Solutions</t>
+        </is>
+      </c>
     </row>
     <row r="704">
       <c r="C704" s="10" t="inlineStr">
@@ -20233,6 +23713,11 @@
           <t>Bhukya Rohith</t>
         </is>
       </c>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="705">
       <c r="C705" s="10" t="inlineStr">
@@ -20261,6 +23746,11 @@
           <t>Nissan Biswas</t>
         </is>
       </c>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
     </row>
     <row r="706">
       <c r="C706" s="10" t="inlineStr">
@@ -20289,6 +23779,11 @@
           <t>Krishan Baghel</t>
         </is>
       </c>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="707">
       <c r="C707" s="10" t="inlineStr">
@@ -20317,6 +23812,11 @@
           <t>Deepanshu</t>
         </is>
       </c>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>ThinkNext</t>
+        </is>
+      </c>
     </row>
     <row r="708">
       <c r="C708" s="10" t="inlineStr">
@@ -20345,6 +23845,11 @@
           <t>Abhinav Bakliwal</t>
         </is>
       </c>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>Microsoft certification</t>
+        </is>
+      </c>
     </row>
     <row r="709">
       <c r="C709" s="10" t="inlineStr">
@@ -20373,6 +23878,11 @@
           <t>Pratham Sharma</t>
         </is>
       </c>
+      <c r="I709" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="710">
       <c r="C710" s="10" t="inlineStr">
@@ -20401,6 +23911,11 @@
           <t>Sekh Alimuddin</t>
         </is>
       </c>
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>Forge</t>
+        </is>
+      </c>
     </row>
     <row r="711">
       <c r="C711" s="10" t="inlineStr">
@@ -20429,6 +23944,11 @@
           <t>Vishavjit Singh</t>
         </is>
       </c>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="712">
       <c r="C712" s="10" t="inlineStr">
@@ -20457,6 +23977,11 @@
           <t>Anurag Mondal</t>
         </is>
       </c>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="713">
       <c r="C713" s="10" t="inlineStr">
@@ -20485,6 +24010,11 @@
           <t>Jasmeet Singh</t>
         </is>
       </c>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="714">
       <c r="C714" s="10" t="inlineStr">
@@ -20513,6 +24043,11 @@
           <t>Arnav Hooda</t>
         </is>
       </c>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>Github</t>
+        </is>
+      </c>
     </row>
     <row r="715">
       <c r="C715" s="10" t="inlineStr">
@@ -20541,6 +24076,11 @@
           <t>Suchitra Panigrahi</t>
         </is>
       </c>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>Tripple One Solutions from IIT Hyderabad</t>
+        </is>
+      </c>
     </row>
     <row r="716">
       <c r="C716" s="10" t="inlineStr">
@@ -20569,6 +24109,11 @@
           <t>Ashish Raj</t>
         </is>
       </c>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>Fortinet</t>
+        </is>
+      </c>
     </row>
     <row r="717">
       <c r="C717" s="10" t="inlineStr">
@@ -20597,6 +24142,11 @@
           <t>Ajitesh Radhwaj Singh</t>
         </is>
       </c>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
     </row>
     <row r="718">
       <c r="C718" s="10" t="inlineStr">
@@ -20625,6 +24175,11 @@
           <t>Shubham mahajan</t>
         </is>
       </c>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
     </row>
     <row r="719">
       <c r="C719" s="10" t="inlineStr">
@@ -20653,6 +24208,11 @@
           <t>Gurbani Aneja</t>
         </is>
       </c>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>Fortinent Certified associate</t>
+        </is>
+      </c>
     </row>
     <row r="720">
       <c r="C720" s="10" t="inlineStr">
@@ -20681,6 +24241,11 @@
           <t>Prianshul kumar</t>
         </is>
       </c>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>Microsoft certification</t>
+        </is>
+      </c>
     </row>
     <row r="721">
       <c r="C721" s="10" t="inlineStr">
@@ -20709,6 +24274,11 @@
           <t>Paras Manak</t>
         </is>
       </c>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
     </row>
     <row r="722">
       <c r="C722" s="10" t="inlineStr">
@@ -20737,6 +24307,11 @@
           <t>Piyush Kumar</t>
         </is>
       </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="723">
       <c r="C723" s="10" t="inlineStr">
@@ -20765,6 +24340,11 @@
           <t>Rahul</t>
         </is>
       </c>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>Microsoft  Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="724">
       <c r="C724" s="10" t="inlineStr">
@@ -20793,6 +24373,11 @@
           <t>Japkirat Kaur</t>
         </is>
       </c>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="725">
       <c r="C725" s="10" t="inlineStr">
@@ -20821,6 +24406,11 @@
           <t>MEHAK</t>
         </is>
       </c>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>Microsoft Github</t>
+        </is>
+      </c>
     </row>
     <row r="726">
       <c r="C726" s="10" t="inlineStr">
@@ -20849,6 +24439,11 @@
           <t>Mannat Mehta</t>
         </is>
       </c>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>Microsoft Certification</t>
+        </is>
+      </c>
     </row>
     <row r="727">
       <c r="C727" s="10" t="inlineStr">
@@ -20877,6 +24472,11 @@
           <t>isha</t>
         </is>
       </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>microsoft cerifications</t>
+        </is>
+      </c>
     </row>
     <row r="728">
       <c r="C728" s="10" t="inlineStr">
@@ -20905,6 +24505,11 @@
           <t>Saket</t>
         </is>
       </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>01/10/2025  to  16/10/2025</t>
+        </is>
+      </c>
     </row>
     <row r="729">
       <c r="C729" s="10" t="inlineStr">
@@ -20933,6 +24538,11 @@
           <t>Md.Mosfiqur Rahman Shuvo</t>
         </is>
       </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>Fortinet Training Institute</t>
+        </is>
+      </c>
     </row>
     <row r="730">
       <c r="C730" s="10" t="inlineStr">
@@ -20961,6 +24571,11 @@
           <t>Tonmoy Chandro Roy</t>
         </is>
       </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>Fortinet Traning Institute</t>
+        </is>
+      </c>
     </row>
     <row r="731">
       <c r="C731" s="10" t="inlineStr">
@@ -20989,6 +24604,11 @@
           <t>Shubneet</t>
         </is>
       </c>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
     </row>
     <row r="732">
       <c r="C732" s="10" t="inlineStr">
@@ -21017,6 +24637,11 @@
           <t>Vandranki Jatin</t>
         </is>
       </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>Microsoft Certifications</t>
+        </is>
+      </c>
     </row>
     <row r="733">
       <c r="C733" s="10" t="inlineStr">
@@ -21045,6 +24670,11 @@
           <t>Mohammad Mehfooz</t>
         </is>
       </c>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>Fortinet</t>
+        </is>
+      </c>
     </row>
     <row r="734">
       <c r="C734" s="10" t="inlineStr">
@@ -21073,6 +24703,11 @@
           <t>Hari krishna Setti</t>
         </is>
       </c>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>PrernaGati &amp; technologies</t>
+        </is>
+      </c>
     </row>
     <row r="735">
       <c r="C735" s="10" t="inlineStr">
@@ -21099,6 +24734,11 @@
       <c r="H735" t="inlineStr">
         <is>
           <t>Yuvraj Singh</t>
+        </is>
+      </c>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>Er. Santosh Kumar, Dr. Sandeep Singh Kang</t>
         </is>
       </c>
     </row>
